--- a/Atlas_Rover_Mk1_制造图纸包_V1.0/采购执行表_Atlas_Rover_Mk1_V1.0.xlsx
+++ b/Atlas_Rover_Mk1_制造图纸包_V1.0/采购执行表_Atlas_Rover_Mk1_V1.0.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="采买执行" sheetId="1" r:id="R1fda334591394782"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="采买执行" sheetId="1" r:id="R15b1871fc8704870"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -421,7 +421,7 @@
         <x:v>ESP32-S3-DualEye-Touch-LCD-1.28 Waveshare 双眼 屏 开发板</x:v>
       </x:c>
       <x:c r="E5" s="14" t="str">
-        <x:v>官方宽度 93.5 mm。可作为车头双眼显示；可通过 GPIO/I2C/PWM 扩展控制电机驱动，但不能直接带电机。板上已有麦克风、音频编解码/功放和喇叭接口；未集成可做车灯的 RGB/WS2812 灯。</x:v>
+        <x:v>官方宽度 93.5 mm。Mk.1 中作为车头双眼/HMI/语音主控，通过 UART 给底盘板下发安全运动意图，不直接带电机。板上已有麦克风、音频编解码/功放和喇叭接口；未集成可做车灯的 RGB/WS2812 灯。</x:v>
       </x:c>
       <x:c r="F5" s="14" t="str">
         <x:v>https://search.jd.com/Search?keyword=ESP32-S3-DualEye-Touch-LCD-1.28%20Waveshare%20%E5%8F%8C%E7%9C%BC%20%E5%B1%8F%20%E5%BC%80%E5%8F%91%E6%9D%BF</x:v>
@@ -435,137 +435,137 @@
     </x:row>
     <x:row r="6" ht="42" customHeight="1">
       <x:c r="A6" s="14" t="str">
-        <x:v>N20 金属减速电机</x:v>
+        <x:v>Seeed Studio XIAO ESP32C3 底盘控制板</x:v>
       </x:c>
       <x:c r="B6" s="14" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C6" s="14" t="str">
         <x:v>必买</x:v>
       </x:c>
       <x:c r="D6" s="14" t="str">
-        <x:v>N20 金属减速电机 6V 100RPM 3mm D轴 轴长10mm</x:v>
+        <x:v>Seeed XIAO ESP32C3 开发板</x:v>
       </x:c>
       <x:c r="E6" s="14" t="str">
-        <x:v>100 RPM 更适合桌面慢速巡游；150 RPM 可用 PWM 限速。Mk.1 不需要编码器版本，除非你要做里程计。</x:v>
+        <x:v>Mk.1 推荐底盘板。负责接收 DualEye UART 的 AR1 指令，执行限速、短时开环差速和超时停车。可用 ESP32-C3 SuperMini 替代，但需要按实物重核引脚。</x:v>
       </x:c>
       <x:c r="F6" s="14" t="str">
-        <x:v>https://search.jd.com/Search?keyword=N20%20%E9%87%91%E5%B1%9E%E5%87%8F%E9%80%9F%E7%94%B5%E6%9C%BA%206V%20100RPM%203mm%20D%E8%BD%B4%20%E8%BD%B4%E9%95%BF10mm</x:v>
+        <x:v>https://search.jd.com/Search?keyword=Seeed%20XIAO%20ESP32C3%20%E5%BC%80%E5%8F%91%E6%9D%BF</x:v>
       </x:c>
       <x:c r="G6" s="14" t="str">
-        <x:v>https://s.taobao.com/search?q=N20%20%E9%87%91%E5%B1%9E%E5%87%8F%E9%80%9F%E7%94%B5%E6%9C%BA%206V%20100RPM%203mm%20D%E8%BD%B4%20%E8%BD%B4%E9%95%BF10mm</x:v>
+        <x:v>https://s.taobao.com/search?q=Seeed%20XIAO%20ESP32C3%20%E5%BC%80%E5%8F%91%E6%9D%BF</x:v>
       </x:c>
       <x:c r="H6" s="14" t="str">
-        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=N20%20%E9%87%91%E5%B1%9E%E5%87%8F%E9%80%9F%E7%94%B5%E6%9C%BA%206V%20100RPM%203mm%20D%E8%BD%B4%20%E8%BD%B4%E9%95%BF10mm</x:v>
+        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=Seeed%20XIAO%20ESP32C3%20%E5%BC%80%E5%8F%91%E6%9D%BF</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="42" customHeight="1">
       <x:c r="A7" s="14" t="str">
-        <x:v>DRV8833 双路 H 桥电机驱动板（必备）</x:v>
+        <x:v>N20 金属减速电机</x:v>
       </x:c>
       <x:c r="B7" s="14" t="str">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C7" s="14" t="str">
         <x:v>必买</x:v>
       </x:c>
       <x:c r="D7" s="14" t="str">
-        <x:v>DRV8833 双路 H桥 电机驱动模块 迷你</x:v>
+        <x:v>N20 金属减速电机 6V 100RPM 3mm D轴 轴长10mm</x:v>
       </x:c>
       <x:c r="E7" s="14" t="str">
-        <x:v>这就是解决“ESP32 不能直接带电机”的必备板子。ESP32/PCA9685 只给控制信号，DRV8833 才负责给 N20 电机输出电流。VM 接电机 5 V 升压支路，逻辑电平接 3.3 V，必须共地。</x:v>
+        <x:v>100 RPM 更适合桌面慢速巡游；150 RPM 可用 PWM 限速。Mk.1 不需要编码器版本，除非你要做里程计。</x:v>
       </x:c>
       <x:c r="F7" s="14" t="str">
-        <x:v>https://search.jd.com/Search?keyword=DRV8833%20%E5%8F%8C%E8%B7%AF%20H%E6%A1%A5%20%E7%94%B5%E6%9C%BA%E9%A9%B1%E5%8A%A8%E6%A8%A1%E5%9D%97%20%E8%BF%B7%E4%BD%A0</x:v>
+        <x:v>https://search.jd.com/Search?keyword=N20%20%E9%87%91%E5%B1%9E%E5%87%8F%E9%80%9F%E7%94%B5%E6%9C%BA%206V%20100RPM%203mm%20D%E8%BD%B4%20%E8%BD%B4%E9%95%BF10mm</x:v>
       </x:c>
       <x:c r="G7" s="14" t="str">
-        <x:v>https://s.taobao.com/search?q=DRV8833%20%E5%8F%8C%E8%B7%AF%20H%E6%A1%A5%20%E7%94%B5%E6%9C%BA%E9%A9%B1%E5%8A%A8%E6%A8%A1%E5%9D%97%20%E8%BF%B7%E4%BD%A0</x:v>
+        <x:v>https://s.taobao.com/search?q=N20%20%E9%87%91%E5%B1%9E%E5%87%8F%E9%80%9F%E7%94%B5%E6%9C%BA%206V%20100RPM%203mm%20D%E8%BD%B4%20%E8%BD%B4%E9%95%BF10mm</x:v>
       </x:c>
       <x:c r="H7" s="14" t="str">
-        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=DRV8833%20%E5%8F%8C%E8%B7%AF%20H%E6%A1%A5%20%E7%94%B5%E6%9C%BA%E9%A9%B1%E5%8A%A8%E6%A8%A1%E5%9D%97%20%E8%BF%B7%E4%BD%A0</x:v>
+        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=N20%20%E9%87%91%E5%B1%9E%E5%87%8F%E9%80%9F%E7%94%B5%E6%9C%BA%206V%20100RPM%203mm%20D%E8%BD%B4%20%E8%BD%B4%E9%95%BF10mm</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="42" customHeight="1">
       <x:c r="A8" s="14" t="str">
-        <x:v>PCA9685 I2C PWM 扩展板（推荐）</x:v>
+        <x:v>DRV8833 双路 H 桥电机驱动板（必备）</x:v>
       </x:c>
       <x:c r="B8" s="14" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C8" s="14" t="str">
-        <x:v>推荐</x:v>
+        <x:v>必买</x:v>
       </x:c>
       <x:c r="D8" s="14" t="str">
-        <x:v>PCA9685 16路 PWM 舵机驱动模块 I2C 迷你</x:v>
+        <x:v>DRV8833 双路 H桥 电机驱动模块 迷你</x:v>
       </x:c>
       <x:c r="E8" s="14" t="str">
-        <x:v>这是控制信号扩展板，不是电机驱动板。它负责给 DRV8833 提供多路 PWM/方向控制信号；如果确认主控板有 4 个可用 GPIO，可省略。</x:v>
+        <x:v>这就是解决“ESP32 不能直接带电机”的必备板子。底盘控制板/PCA9685 只给控制信号，DRV8833 才负责给 N20 电机输出电流。VM 接电机 5 V 升压支路，逻辑电平接 3.3 V，必须共地。</x:v>
       </x:c>
       <x:c r="F8" s="14" t="str">
-        <x:v>https://search.jd.com/Search?keyword=PCA9685%2016%E8%B7%AF%20PWM%20%E8%88%B5%E6%9C%BA%E9%A9%B1%E5%8A%A8%E6%A8%A1%E5%9D%97%20I2C%20%E8%BF%B7%E4%BD%A0</x:v>
+        <x:v>https://search.jd.com/Search?keyword=DRV8833%20%E5%8F%8C%E8%B7%AF%20H%E6%A1%A5%20%E7%94%B5%E6%9C%BA%E9%A9%B1%E5%8A%A8%E6%A8%A1%E5%9D%97%20%E8%BF%B7%E4%BD%A0</x:v>
       </x:c>
       <x:c r="G8" s="14" t="str">
-        <x:v>https://s.taobao.com/search?q=PCA9685%2016%E8%B7%AF%20PWM%20%E8%88%B5%E6%9C%BA%E9%A9%B1%E5%8A%A8%E6%A8%A1%E5%9D%97%20I2C%20%E8%BF%B7%E4%BD%A0</x:v>
+        <x:v>https://s.taobao.com/search?q=DRV8833%20%E5%8F%8C%E8%B7%AF%20H%E6%A1%A5%20%E7%94%B5%E6%9C%BA%E9%A9%B1%E5%8A%A8%E6%A8%A1%E5%9D%97%20%E8%BF%B7%E4%BD%A0</x:v>
       </x:c>
       <x:c r="H8" s="14" t="str">
-        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=PCA9685%2016%E8%B7%AF%20PWM%20%E8%88%B5%E6%9C%BA%E9%A9%B1%E5%8A%A8%E6%A8%A1%E5%9D%97%20I2C%20%E8%BF%B7%E4%BD%A0</x:v>
+        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=DRV8833%20%E5%8F%8C%E8%B7%AF%20H%E6%A1%A5%20%E7%94%B5%E6%9C%BA%E9%A9%B1%E5%8A%A8%E6%A8%A1%E5%9D%97%20%E8%BF%B7%E4%BD%A0</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="42" customHeight="1">
       <x:c r="A9" s="14" t="str">
-        <x:v>N20 轮胎</x:v>
+        <x:v>PCA9685 I2C PWM 扩展板（推荐）</x:v>
       </x:c>
       <x:c r="B9" s="14" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C9" s="14" t="str">
-        <x:v>必买</x:v>
+        <x:v>推荐</x:v>
       </x:c>
       <x:c r="D9" s="14" t="str">
-        <x:v>N20 轮胎 34mm 3mm D形孔 橡胶轮</x:v>
+        <x:v>PCA9685 16路 PWM 舵机驱动模块 I2C 迷你</x:v>
       </x:c>
       <x:c r="E9" s="14" t="str">
-        <x:v>43 mm 轮也能用，但要抬高前保险杠，并且速度和外宽都会增加。</x:v>
+        <x:v>这是底盘板侧可选控制信号扩展板，不是电机驱动板。若底盘控制板已有 4 个可用 PWM/DIR GPIO，可省略。</x:v>
       </x:c>
       <x:c r="F9" s="14" t="str">
-        <x:v>https://search.jd.com/Search?keyword=N20%20%E8%BD%AE%E8%83%8E%2034mm%203mm%20D%E5%BD%A2%E5%AD%94%20%E6%A9%A1%E8%83%B6%E8%BD%AE</x:v>
+        <x:v>https://search.jd.com/Search?keyword=PCA9685%2016%E8%B7%AF%20PWM%20%E8%88%B5%E6%9C%BA%E9%A9%B1%E5%8A%A8%E6%A8%A1%E5%9D%97%20I2C%20%E8%BF%B7%E4%BD%A0</x:v>
       </x:c>
       <x:c r="G9" s="14" t="str">
-        <x:v>https://s.taobao.com/search?q=N20%20%E8%BD%AE%E8%83%8E%2034mm%203mm%20D%E5%BD%A2%E5%AD%94%20%E6%A9%A1%E8%83%B6%E8%BD%AE</x:v>
+        <x:v>https://s.taobao.com/search?q=PCA9685%2016%E8%B7%AF%20PWM%20%E8%88%B5%E6%9C%BA%E9%A9%B1%E5%8A%A8%E6%A8%A1%E5%9D%97%20I2C%20%E8%BF%B7%E4%BD%A0</x:v>
       </x:c>
       <x:c r="H9" s="14" t="str">
-        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=N20%20%E8%BD%AE%E8%83%8E%2034mm%203mm%20D%E5%BD%A2%E5%AD%94%20%E6%A9%A1%E8%83%B6%E8%BD%AE</x:v>
+        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=PCA9685%2016%E8%B7%AF%20PWM%20%E8%88%B5%E6%9C%BA%E9%A9%B1%E5%8A%A8%E6%A8%A1%E5%9D%97%20I2C%20%E8%BF%B7%E4%BD%A0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="42" customHeight="1">
       <x:c r="A10" s="14" t="str">
-        <x:v>迷你万向轮</x:v>
+        <x:v>N20 轮胎</x:v>
       </x:c>
       <x:c r="B10" s="14" t="str">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C10" s="14" t="str">
         <x:v>必买</x:v>
       </x:c>
       <x:c r="D10" s="14" t="str">
-        <x:v>迷你万向轮 10mm 15mm 球形 小车</x:v>
+        <x:v>N20 轮胎 34mm 3mm D形孔 橡胶轮</x:v>
       </x:c>
       <x:c r="E10" s="14" t="str">
-        <x:v>前置万向轮能让第一版结构更简单。若底盘不水平，可加 1-2 mm 垫片。</x:v>
+        <x:v>43 mm 轮也能用，但要抬高前保险杠，并且速度和外宽都会增加。</x:v>
       </x:c>
       <x:c r="F10" s="14" t="str">
-        <x:v>https://search.jd.com/Search?keyword=%E8%BF%B7%E4%BD%A0%E4%B8%87%E5%90%91%E8%BD%AE%2010mm%2015mm%20%E7%90%83%E5%BD%A2%20%E5%B0%8F%E8%BD%A6</x:v>
+        <x:v>https://search.jd.com/Search?keyword=N20%20%E8%BD%AE%E8%83%8E%2034mm%203mm%20D%E5%BD%A2%E5%AD%94%20%E6%A9%A1%E8%83%B6%E8%BD%AE</x:v>
       </x:c>
       <x:c r="G10" s="14" t="str">
-        <x:v>https://s.taobao.com/search?q=%E8%BF%B7%E4%BD%A0%E4%B8%87%E5%90%91%E8%BD%AE%2010mm%2015mm%20%E7%90%83%E5%BD%A2%20%E5%B0%8F%E8%BD%A6</x:v>
+        <x:v>https://s.taobao.com/search?q=N20%20%E8%BD%AE%E8%83%8E%2034mm%203mm%20D%E5%BD%A2%E5%AD%94%20%E6%A9%A1%E8%83%B6%E8%BD%AE</x:v>
       </x:c>
       <x:c r="H10" s="14" t="str">
-        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=%E8%BF%B7%E4%BD%A0%E4%B8%87%E5%90%91%E8%BD%AE%2010mm%2015mm%20%E7%90%83%E5%BD%A2%20%E5%B0%8F%E8%BD%A6</x:v>
+        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=N20%20%E8%BD%AE%E8%83%8E%2034mm%203mm%20D%E5%BD%A2%E5%AD%94%20%E6%A9%A1%E8%83%B6%E8%BD%AE</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="42" customHeight="1">
       <x:c r="A11" s="14" t="str">
-        <x:v>18650 锂电池</x:v>
+        <x:v>迷你万向轮</x:v>
       </x:c>
       <x:c r="B11" s="14" t="str">
         <x:v>1</x:v>
@@ -574,24 +574,24 @@
         <x:v>必买</x:v>
       </x:c>
       <x:c r="D11" s="14" t="str">
-        <x:v>18650 锂电池 3.7V 2600mAh 带保护板 持续放电3A</x:v>
+        <x:v>迷你万向轮 10mm 15mm 球形 小车</x:v>
       </x:c>
       <x:c r="E11" s="14" t="str">
-        <x:v>裸电芯约 18 x 65 mm；带保护板或尖头电芯可能更长。避免虚标容量电池，电机启动电流会拉低电压。</x:v>
+        <x:v>前置万向轮能让第一版结构更简单。若底盘不水平，可加 1-2 mm 垫片。</x:v>
       </x:c>
       <x:c r="F11" s="14" t="str">
-        <x:v>https://search.jd.com/Search?keyword=18650%20%E9%94%82%E7%94%B5%E6%B1%A0%203.7V%202600mAh%20%E5%B8%A6%E4%BF%9D%E6%8A%A4%E6%9D%BF%20%E6%8C%81%E7%BB%AD%E6%94%BE%E7%94%B53A</x:v>
+        <x:v>https://search.jd.com/Search?keyword=%E8%BF%B7%E4%BD%A0%E4%B8%87%E5%90%91%E8%BD%AE%2010mm%2015mm%20%E7%90%83%E5%BD%A2%20%E5%B0%8F%E8%BD%A6</x:v>
       </x:c>
       <x:c r="G11" s="14" t="str">
-        <x:v>https://s.taobao.com/search?q=18650%20%E9%94%82%E7%94%B5%E6%B1%A0%203.7V%202600mAh%20%E5%B8%A6%E4%BF%9D%E6%8A%A4%E6%9D%BF%20%E6%8C%81%E7%BB%AD%E6%94%BE%E7%94%B53A</x:v>
+        <x:v>https://s.taobao.com/search?q=%E8%BF%B7%E4%BD%A0%E4%B8%87%E5%90%91%E8%BD%AE%2010mm%2015mm%20%E7%90%83%E5%BD%A2%20%E5%B0%8F%E8%BD%A6</x:v>
       </x:c>
       <x:c r="H11" s="14" t="str">
-        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=18650%20%E9%94%82%E7%94%B5%E6%B1%A0%203.7V%202600mAh%20%E5%B8%A6%E4%BF%9D%E6%8A%A4%E6%9D%BF%20%E6%8C%81%E7%BB%AD%E6%94%BE%E7%94%B53A</x:v>
+        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=%E8%BF%B7%E4%BD%A0%E4%B8%87%E5%90%91%E8%BD%AE%2010mm%2015mm%20%E7%90%83%E5%BD%A2%20%E5%B0%8F%E8%BD%A6</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="42" customHeight="1">
       <x:c r="A12" s="14" t="str">
-        <x:v>单节 18650 电池盒带线</x:v>
+        <x:v>18650 锂电池</x:v>
       </x:c>
       <x:c r="B12" s="14" t="str">
         <x:v>1</x:v>
@@ -600,24 +600,24 @@
         <x:v>必买</x:v>
       </x:c>
       <x:c r="D12" s="14" t="str">
-        <x:v>单节 18650 电池盒 带线 1节</x:v>
+        <x:v>18650 锂电池 3.7V 2600mAh 带保护板 持续放电3A</x:v>
       </x:c>
       <x:c r="E12" s="14" t="str">
-        <x:v>沿底层长度方向安装。双节电池盒不属于 Mk.1 方案。</x:v>
+        <x:v>裸电芯约 18 x 65 mm；带保护板或尖头电芯可能更长。避免虚标容量电池，电机启动电流会拉低电压。</x:v>
       </x:c>
       <x:c r="F12" s="14" t="str">
-        <x:v>https://search.jd.com/Search?keyword=%E5%8D%95%E8%8A%82%2018650%20%E7%94%B5%E6%B1%A0%E7%9B%92%20%E5%B8%A6%E7%BA%BF%201%E8%8A%82</x:v>
+        <x:v>https://search.jd.com/Search?keyword=18650%20%E9%94%82%E7%94%B5%E6%B1%A0%203.7V%202600mAh%20%E5%B8%A6%E4%BF%9D%E6%8A%A4%E6%9D%BF%20%E6%8C%81%E7%BB%AD%E6%94%BE%E7%94%B53A</x:v>
       </x:c>
       <x:c r="G12" s="14" t="str">
-        <x:v>https://s.taobao.com/search?q=%E5%8D%95%E8%8A%82%2018650%20%E7%94%B5%E6%B1%A0%E7%9B%92%20%E5%B8%A6%E7%BA%BF%201%E8%8A%82</x:v>
+        <x:v>https://s.taobao.com/search?q=18650%20%E9%94%82%E7%94%B5%E6%B1%A0%203.7V%202600mAh%20%E5%B8%A6%E4%BF%9D%E6%8A%A4%E6%9D%BF%20%E6%8C%81%E7%BB%AD%E6%94%BE%E7%94%B53A</x:v>
       </x:c>
       <x:c r="H12" s="14" t="str">
-        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=%E5%8D%95%E8%8A%82%2018650%20%E7%94%B5%E6%B1%A0%E7%9B%92%20%E5%B8%A6%E7%BA%BF%201%E8%8A%82</x:v>
+        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=18650%20%E9%94%82%E7%94%B5%E6%B1%A0%203.7V%202600mAh%20%E5%B8%A6%E4%BF%9D%E6%8A%A4%E6%9D%BF%20%E6%8C%81%E7%BB%AD%E6%94%BE%E7%94%B53A</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="42" customHeight="1">
       <x:c r="A13" s="14" t="str">
-        <x:v>5 V 升压模块</x:v>
+        <x:v>单节 18650 电池盒带线</x:v>
       </x:c>
       <x:c r="B13" s="14" t="str">
         <x:v>1</x:v>
@@ -626,76 +626,76 @@
         <x:v>必买</x:v>
       </x:c>
       <x:c r="D13" s="14" t="str">
-        <x:v>锂电池升压模块 3.7V转5V 2A 3A</x:v>
+        <x:v>单节 18650 电池盒 带线 1节</x:v>
       </x:c>
       <x:c r="E13" s="14" t="str">
-        <x:v>只给电机支路使用。不要让电机电流经过 ESP32 的 3.3 V 电源轨。若两个 N20 堵转明显，优先换更大电流模块。</x:v>
+        <x:v>沿底层长度方向安装。双节电池盒不属于 Mk.1 方案。</x:v>
       </x:c>
       <x:c r="F13" s="14" t="str">
-        <x:v>https://search.jd.com/Search?keyword=%E9%94%82%E7%94%B5%E6%B1%A0%E5%8D%87%E5%8E%8B%E6%A8%A1%E5%9D%97%203.7V%E8%BD%AC5V%202A%203A</x:v>
+        <x:v>https://search.jd.com/Search?keyword=%E5%8D%95%E8%8A%82%2018650%20%E7%94%B5%E6%B1%A0%E7%9B%92%20%E5%B8%A6%E7%BA%BF%201%E8%8A%82</x:v>
       </x:c>
       <x:c r="G13" s="14" t="str">
-        <x:v>https://s.taobao.com/search?q=%E9%94%82%E7%94%B5%E6%B1%A0%E5%8D%87%E5%8E%8B%E6%A8%A1%E5%9D%97%203.7V%E8%BD%AC5V%202A%203A</x:v>
+        <x:v>https://s.taobao.com/search?q=%E5%8D%95%E8%8A%82%2018650%20%E7%94%B5%E6%B1%A0%E7%9B%92%20%E5%B8%A6%E7%BA%BF%201%E8%8A%82</x:v>
       </x:c>
       <x:c r="H13" s="14" t="str">
-        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=%E9%94%82%E7%94%B5%E6%B1%A0%E5%8D%87%E5%8E%8B%E6%A8%A1%E5%9D%97%203.7V%E8%BD%AC5V%202A%203A</x:v>
+        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=%E5%8D%95%E8%8A%82%2018650%20%E7%94%B5%E6%B1%A0%E7%9B%92%20%E5%B8%A6%E7%BA%BF%201%E8%8A%82</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="42" customHeight="1">
       <x:c r="A14" s="14" t="str">
-        <x:v>电源开关与保护</x:v>
+        <x:v>5 V 升压模块</x:v>
       </x:c>
       <x:c r="B14" s="14" t="str">
-        <x:v>1 套</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C14" s="14" t="str">
         <x:v>必买</x:v>
       </x:c>
       <x:c r="D14" s="14" t="str">
-        <x:v>迷你拨动开关 1S 18650 保护板 3.7V</x:v>
+        <x:v>锂电池升压模块 3.7V转5V 2A 3A</x:v>
       </x:c>
       <x:c r="E14" s="14" t="str">
-        <x:v>只保留一条充电路径。除非电池路径隔离，不要把 TP4056 与板载充电并联。</x:v>
+        <x:v>只给电机支路使用。不要让电机电流经过 ESP32 的 3.3 V 电源轨。若两个 N20 堵转明显，优先换更大电流模块。</x:v>
       </x:c>
       <x:c r="F14" s="14" t="str">
-        <x:v>https://search.jd.com/Search?keyword=%E8%BF%B7%E4%BD%A0%E6%8B%A8%E5%8A%A8%E5%BC%80%E5%85%B3%201S%2018650%20%E4%BF%9D%E6%8A%A4%E6%9D%BF%203.7V</x:v>
+        <x:v>https://search.jd.com/Search?keyword=%E9%94%82%E7%94%B5%E6%B1%A0%E5%8D%87%E5%8E%8B%E6%A8%A1%E5%9D%97%203.7V%E8%BD%AC5V%202A%203A</x:v>
       </x:c>
       <x:c r="G14" s="14" t="str">
-        <x:v>https://s.taobao.com/search?q=%E8%BF%B7%E4%BD%A0%E6%8B%A8%E5%8A%A8%E5%BC%80%E5%85%B3%201S%2018650%20%E4%BF%9D%E6%8A%A4%E6%9D%BF%203.7V</x:v>
+        <x:v>https://s.taobao.com/search?q=%E9%94%82%E7%94%B5%E6%B1%A0%E5%8D%87%E5%8E%8B%E6%A8%A1%E5%9D%97%203.7V%E8%BD%AC5V%202A%203A</x:v>
       </x:c>
       <x:c r="H14" s="14" t="str">
-        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=%E8%BF%B7%E4%BD%A0%E6%8B%A8%E5%8A%A8%E5%BC%80%E5%85%B3%201S%2018650%20%E4%BF%9D%E6%8A%A4%E6%9D%BF%203.7V</x:v>
+        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=%E9%94%82%E7%94%B5%E6%B1%A0%E5%8D%87%E5%8E%8B%E6%A8%A1%E5%9D%97%203.7V%E8%BD%AC5V%202A%203A</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="42" customHeight="1">
       <x:c r="A15" s="14" t="str">
-        <x:v>小喇叭</x:v>
+        <x:v>电源开关与保护</x:v>
       </x:c>
       <x:c r="B15" s="14" t="str">
-        <x:v>1</x:v>
+        <x:v>1 套</x:v>
       </x:c>
       <x:c r="C15" s="14" t="str">
-        <x:v>推荐</x:v>
+        <x:v>必买</x:v>
       </x:c>
       <x:c r="D15" s="14" t="str">
-        <x:v>4欧3W 小喇叭 直径40mm 以下</x:v>
+        <x:v>迷你拨动开关 1S 18650 保护板 3.7V</x:v>
       </x:c>
       <x:c r="E15" s="14" t="str">
-        <x:v>主控板已有麦克风、音频编解码、功放和喇叭接口；但通常仍需外接一个小喇叭才能外放。Mk.1 不必购买 MAX98357A 和 INMP441。</x:v>
+        <x:v>只保留一条充电路径。除非电池路径隔离，不要把 TP4056 与板载充电并联。</x:v>
       </x:c>
       <x:c r="F15" s="14" t="str">
-        <x:v>https://search.jd.com/Search?keyword=4%E6%AC%A73W%20%E5%B0%8F%E5%96%87%E5%8F%AD%20%E7%9B%B4%E5%BE%8440mm%20%E4%BB%A5%E4%B8%8B</x:v>
+        <x:v>https://search.jd.com/Search?keyword=%E8%BF%B7%E4%BD%A0%E6%8B%A8%E5%8A%A8%E5%BC%80%E5%85%B3%201S%2018650%20%E4%BF%9D%E6%8A%A4%E6%9D%BF%203.7V</x:v>
       </x:c>
       <x:c r="G15" s="14" t="str">
-        <x:v>https://s.taobao.com/search?q=4%E6%AC%A73W%20%E5%B0%8F%E5%96%87%E5%8F%AD%20%E7%9B%B4%E5%BE%8440mm%20%E4%BB%A5%E4%B8%8B</x:v>
+        <x:v>https://s.taobao.com/search?q=%E8%BF%B7%E4%BD%A0%E6%8B%A8%E5%8A%A8%E5%BC%80%E5%85%B3%201S%2018650%20%E4%BF%9D%E6%8A%A4%E6%9D%BF%203.7V</x:v>
       </x:c>
       <x:c r="H15" s="14" t="str">
-        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=4%E6%AC%A73W%20%E5%B0%8F%E5%96%87%E5%8F%AD%20%E7%9B%B4%E5%BE%8440mm%20%E4%BB%A5%E4%B8%8B</x:v>
+        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=%E8%BF%B7%E4%BD%A0%E6%8B%A8%E5%8A%A8%E5%BC%80%E5%85%B3%201S%2018650%20%E4%BF%9D%E6%8A%A4%E6%9D%BF%203.7V</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="42" customHeight="1">
       <x:c r="A16" s="14" t="str">
-        <x:v>WS2812B 灯条或灯环（外接车灯模块）</x:v>
+        <x:v>小喇叭</x:v>
       </x:c>
       <x:c r="B16" s="14" t="str">
         <x:v>1</x:v>
@@ -704,24 +704,24 @@
         <x:v>推荐</x:v>
       </x:c>
       <x:c r="D16" s="14" t="str">
-        <x:v>WS2812B 8位 灯环 5V 30mm</x:v>
+        <x:v>4欧3W 小喇叭 直径40mm 以下</x:v>
       </x:c>
       <x:c r="E16" s="14" t="str">
-        <x:v>这就是解决“没有集成车灯/RGB”的外接灯光模块。需要 5 V、GND 和 1 个数据 GPIO；8 颗灯全白约 0.48 A，建议限亮度并加 330 欧数据电阻和 470-1000 uF 电容。</x:v>
+        <x:v>主控板已有麦克风、音频编解码、功放和喇叭接口；但通常仍需外接一个小喇叭才能外放。Mk.1 不必购买 MAX98357A 和 INMP441。</x:v>
       </x:c>
       <x:c r="F16" s="14" t="str">
-        <x:v>https://search.jd.com/Search?keyword=WS2812B%208%E4%BD%8D%20%E7%81%AF%E7%8E%AF%205V%2030mm</x:v>
+        <x:v>https://search.jd.com/Search?keyword=4%E6%AC%A73W%20%E5%B0%8F%E5%96%87%E5%8F%AD%20%E7%9B%B4%E5%BE%8440mm%20%E4%BB%A5%E4%B8%8B</x:v>
       </x:c>
       <x:c r="G16" s="14" t="str">
-        <x:v>https://s.taobao.com/search?q=WS2812B%208%E4%BD%8D%20%E7%81%AF%E7%8E%AF%205V%2030mm</x:v>
+        <x:v>https://s.taobao.com/search?q=4%E6%AC%A73W%20%E5%B0%8F%E5%96%87%E5%8F%AD%20%E7%9B%B4%E5%BE%8440mm%20%E4%BB%A5%E4%B8%8B</x:v>
       </x:c>
       <x:c r="H16" s="14" t="str">
-        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=WS2812B%208%E4%BD%8D%20%E7%81%AF%E7%8E%AF%205V%2030mm</x:v>
+        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=4%E6%AC%A73W%20%E5%B0%8F%E5%96%87%E5%8F%AD%20%E7%9B%B4%E5%BE%8440mm%20%E4%BB%A5%E4%B8%8B</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="42" customHeight="1">
       <x:c r="A17" s="14" t="str">
-        <x:v>WS2812B 数据电平转换器（推荐）</x:v>
+        <x:v>WS2812B 灯条或灯环（外接车灯模块）</x:v>
       </x:c>
       <x:c r="B17" s="14" t="str">
         <x:v>1</x:v>
@@ -730,50 +730,50 @@
         <x:v>推荐</x:v>
       </x:c>
       <x:c r="D17" s="14" t="str">
-        <x:v>SN74AHCT1G125 74AHCT125 74HCT14 3.3V转5V 电平转换</x:v>
+        <x:v>WS2812B 8位 灯环 5V 30mm</x:v>
       </x:c>
       <x:c r="E17" s="14" t="str">
-        <x:v>WS2812B 用 5 V 供电时，数据高电平按规格需要接近 3.5 V；ESP32 的 3.3 V 短线常能跑，但不够稳。推荐用 AHCT/HCT 电平转换：A 接 ESP32 数据 GPIO，Y 经 330 欧到 DIN，芯片 VCC 接 5 V，GND 共地。</x:v>
+        <x:v>这就是解决“没有集成车灯/RGB”的外接灯光模块。需要 5 V、GND 和 1 个数据 GPIO；8 颗灯全白约 0.48 A，建议限亮度并加 330 欧数据电阻和 470-1000 uF 电容。</x:v>
       </x:c>
       <x:c r="F17" s="14" t="str">
-        <x:v>https://search.jd.com/Search?keyword=SN74AHCT1G125%2074AHCT125%2074HCT14%203.3V%E8%BD%AC5V%20%E7%94%B5%E5%B9%B3%E8%BD%AC%E6%8D%A2</x:v>
+        <x:v>https://search.jd.com/Search?keyword=WS2812B%208%E4%BD%8D%20%E7%81%AF%E7%8E%AF%205V%2030mm</x:v>
       </x:c>
       <x:c r="G17" s="14" t="str">
-        <x:v>https://s.taobao.com/search?q=SN74AHCT1G125%2074AHCT125%2074HCT14%203.3V%E8%BD%AC5V%20%E7%94%B5%E5%B9%B3%E8%BD%AC%E6%8D%A2</x:v>
+        <x:v>https://s.taobao.com/search?q=WS2812B%208%E4%BD%8D%20%E7%81%AF%E7%8E%AF%205V%2030mm</x:v>
       </x:c>
       <x:c r="H17" s="14" t="str">
-        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=SN74AHCT1G125%2074AHCT125%2074HCT14%203.3V%E8%BD%AC5V%20%E7%94%B5%E5%B9%B3%E8%BD%AC%E6%8D%A2</x:v>
+        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=WS2812B%208%E4%BD%8D%20%E7%81%AF%E7%8E%AF%205V%2030mm</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="42" customHeight="1">
       <x:c r="A18" s="14" t="str">
-        <x:v>黄铜丝/黄铜棒</x:v>
+        <x:v>WS2812B 数据电平转换器（推荐）</x:v>
       </x:c>
       <x:c r="B18" s="14" t="str">
-        <x:v>1 套</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C18" s="14" t="str">
-        <x:v>必买</x:v>
+        <x:v>推荐</x:v>
       </x:c>
       <x:c r="D18" s="14" t="str">
-        <x:v>黄铜棒 2mm 3米 1.5mm 2米 1mm 黄铜丝 模型 DIY</x:v>
+        <x:v>SN74AHCT1G125 74AHCT125 74HCT14 3.3V转5V 电平转换</x:v>
       </x:c>
       <x:c r="E18" s="14" t="str">
-        <x:v>2.0 mm 做底框、护栏、立柱和顶部提手；1.5 mm 做护眼圈、斜撑和灯架；1.0 mm 只用于绑扎焊点或装饰，不承担主结构。焊接前预上锡，铜架必须与带电焊盘绝缘。</x:v>
+        <x:v>WS2812B 用 5 V 供电时，数据高电平按规格需要接近 3.5 V；ESP32 的 3.3 V 短线常能跑，但不够稳。推荐用 AHCT/HCT 电平转换：A 接 ESP32 数据 GPIO，Y 经 330 欧到 DIN，芯片 VCC 接 5 V，GND 共地。</x:v>
       </x:c>
       <x:c r="F18" s="14" t="str">
-        <x:v>https://search.jd.com/Search?keyword=%E9%BB%84%E9%93%9C%E6%A3%92%202mm%203%E7%B1%B3%201.5mm%202%E7%B1%B3%201mm%20%E9%BB%84%E9%93%9C%E4%B8%9D%20%E6%A8%A1%E5%9E%8B%20DIY</x:v>
+        <x:v>https://search.jd.com/Search?keyword=SN74AHCT1G125%2074AHCT125%2074HCT14%203.3V%E8%BD%AC5V%20%E7%94%B5%E5%B9%B3%E8%BD%AC%E6%8D%A2</x:v>
       </x:c>
       <x:c r="G18" s="14" t="str">
-        <x:v>https://s.taobao.com/search?q=%E9%BB%84%E9%93%9C%E6%A3%92%202mm%203%E7%B1%B3%201.5mm%202%E7%B1%B3%201mm%20%E9%BB%84%E9%93%9C%E4%B8%9D%20%E6%A8%A1%E5%9E%8B%20DIY</x:v>
+        <x:v>https://s.taobao.com/search?q=SN74AHCT1G125%2074AHCT125%2074HCT14%203.3V%E8%BD%AC5V%20%E7%94%B5%E5%B9%B3%E8%BD%AC%E6%8D%A2</x:v>
       </x:c>
       <x:c r="H18" s="14" t="str">
-        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=%E9%BB%84%E9%93%9C%E6%A3%92%202mm%203%E7%B1%B3%201.5mm%202%E7%B1%B3%201mm%20%E9%BB%84%E9%93%9C%E4%B8%9D%20%E6%A8%A1%E5%9E%8B%20DIY</x:v>
+        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=SN74AHCT1G125%2074AHCT125%2074HCT14%203.3V%E8%BD%AC5V%20%E7%94%B5%E5%B9%B3%E8%BD%AC%E6%8D%A2</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="42" customHeight="1">
       <x:c r="A19" s="14" t="str">
-        <x:v>M2 铜柱套装</x:v>
+        <x:v>黄铜丝/黄铜棒</x:v>
       </x:c>
       <x:c r="B19" s="14" t="str">
         <x:v>1 套</x:v>
@@ -782,76 +782,76 @@
         <x:v>必买</x:v>
       </x:c>
       <x:c r="D19" s="14" t="str">
-        <x:v>M2 铜柱套装 双通 6 8 10 12 15 20mm 螺丝</x:v>
+        <x:v>黄铜棒 2mm 3米 1.5mm 2米 1mm 黄铜丝 模型 DIY</x:v>
       </x:c>
       <x:c r="E19" s="14" t="str">
-        <x:v>用 M2，不用 M3。双眼主控板官方安装孔为 M2。</x:v>
+        <x:v>2.0 mm 做底框、护栏、立柱和顶部提手；1.5 mm 做护眼圈、斜撑和灯架；1.0 mm 只用于绑扎焊点或装饰，不承担主结构。焊接前预上锡，铜架必须与带电焊盘绝缘。</x:v>
       </x:c>
       <x:c r="F19" s="14" t="str">
-        <x:v>https://search.jd.com/Search?keyword=M2%20%E9%93%9C%E6%9F%B1%E5%A5%97%E8%A3%85%20%E5%8F%8C%E9%80%9A%206%208%2010%2012%2015%2020mm%20%E8%9E%BA%E4%B8%9D</x:v>
+        <x:v>https://search.jd.com/Search?keyword=%E9%BB%84%E9%93%9C%E6%A3%92%202mm%203%E7%B1%B3%201.5mm%202%E7%B1%B3%201mm%20%E9%BB%84%E9%93%9C%E4%B8%9D%20%E6%A8%A1%E5%9E%8B%20DIY</x:v>
       </x:c>
       <x:c r="G19" s="14" t="str">
-        <x:v>https://s.taobao.com/search?q=M2%20%E9%93%9C%E6%9F%B1%E5%A5%97%E8%A3%85%20%E5%8F%8C%E9%80%9A%206%208%2010%2012%2015%2020mm%20%E8%9E%BA%E4%B8%9D</x:v>
+        <x:v>https://s.taobao.com/search?q=%E9%BB%84%E9%93%9C%E6%A3%92%202mm%203%E7%B1%B3%201.5mm%202%E7%B1%B3%201mm%20%E9%BB%84%E9%93%9C%E4%B8%9D%20%E6%A8%A1%E5%9E%8B%20DIY</x:v>
       </x:c>
       <x:c r="H19" s="14" t="str">
-        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=M2%20%E9%93%9C%E6%9F%B1%E5%A5%97%E8%A3%85%20%E5%8F%8C%E9%80%9A%206%208%2010%2012%2015%2020mm%20%E8%9E%BA%E4%B8%9D</x:v>
+        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=%E9%BB%84%E9%93%9C%E6%A3%92%202mm%203%E7%B1%B3%201.5mm%202%E7%B1%B3%201mm%20%E9%BB%84%E9%93%9C%E4%B8%9D%20%E6%A8%A1%E5%9E%8B%20DIY</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="42" customHeight="1">
       <x:c r="A20" s="14" t="str">
-        <x:v>层板材料</x:v>
+        <x:v>M2 铜柱套装</x:v>
       </x:c>
       <x:c r="B20" s="14" t="str">
-        <x:v>2</x:v>
+        <x:v>1 套</x:v>
       </x:c>
       <x:c r="C20" s="14" t="str">
         <x:v>必买</x:v>
       </x:c>
       <x:c r="D20" s="14" t="str">
-        <x:v>FR4 洞洞板 2mm 110x72 84x58 亚克力板</x:v>
+        <x:v>M2 铜柱套装 双通 6 8 10 12 15 20mm 螺丝</x:v>
       </x:c>
       <x:c r="E20" s="14" t="str">
-        <x:v>FR4 洞洞板更适合手工钻孔；亚克力更好看，但加工过急容易裂。</x:v>
+        <x:v>用 M2，不用 M3。双眼主控板官方安装孔为 M2。</x:v>
       </x:c>
       <x:c r="F20" s="14" t="str">
-        <x:v>https://search.jd.com/Search?keyword=FR4%20%E6%B4%9E%E6%B4%9E%E6%9D%BF%202mm%20110x72%2084x58%20%E4%BA%9A%E5%85%8B%E5%8A%9B%E6%9D%BF</x:v>
+        <x:v>https://search.jd.com/Search?keyword=M2%20%E9%93%9C%E6%9F%B1%E5%A5%97%E8%A3%85%20%E5%8F%8C%E9%80%9A%206%208%2010%2012%2015%2020mm%20%E8%9E%BA%E4%B8%9D</x:v>
       </x:c>
       <x:c r="G20" s="14" t="str">
-        <x:v>https://s.taobao.com/search?q=FR4%20%E6%B4%9E%E6%B4%9E%E6%9D%BF%202mm%20110x72%2084x58%20%E4%BA%9A%E5%85%8B%E5%8A%9B%E6%9D%BF</x:v>
+        <x:v>https://s.taobao.com/search?q=M2%20%E9%93%9C%E6%9F%B1%E5%A5%97%E8%A3%85%20%E5%8F%8C%E9%80%9A%206%208%2010%2012%2015%2020mm%20%E8%9E%BA%E4%B8%9D</x:v>
       </x:c>
       <x:c r="H20" s="14" t="str">
-        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=FR4%20%E6%B4%9E%E6%B4%9E%E6%9D%BF%202mm%20110x72%2084x58%20%E4%BA%9A%E5%85%8B%E5%8A%9B%E6%9D%BF</x:v>
+        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=M2%20%E9%93%9C%E6%9F%B1%E5%A5%97%E8%A3%85%20%E5%8F%8C%E9%80%9A%206%208%2010%2012%2015%2020mm%20%E8%9E%BA%E4%B8%9D</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="42" customHeight="1">
       <x:c r="A21" s="14" t="str">
-        <x:v>JST/杜邦线套装</x:v>
+        <x:v>层板材料</x:v>
       </x:c>
       <x:c r="B21" s="14" t="str">
-        <x:v>1 套</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C21" s="14" t="str">
         <x:v>必买</x:v>
       </x:c>
       <x:c r="D21" s="14" t="str">
-        <x:v>MX1.25 2P 电池线 SH1.0 14P 转接线 28AWG 杜邦线</x:v>
+        <x:v>FR4 洞洞板 2mm 110x72 84x58 亚克力板</x:v>
       </x:c>
       <x:c r="E21" s="14" t="str">
-        <x:v>主控板外露接口是小间距 SH1.0/FPC 形态，建议准备转接线或转接板；否则手工接线会很难。</x:v>
+        <x:v>FR4 洞洞板更适合手工钻孔；亚克力更好看，但加工过急容易裂。</x:v>
       </x:c>
       <x:c r="F21" s="14" t="str">
-        <x:v>https://search.jd.com/Search?keyword=MX1.25%202P%20%E7%94%B5%E6%B1%A0%E7%BA%BF%20SH1.0%2014P%20%E8%BD%AC%E6%8E%A5%E7%BA%BF%2028AWG%20%E6%9D%9C%E9%82%A6%E7%BA%BF</x:v>
+        <x:v>https://search.jd.com/Search?keyword=FR4%20%E6%B4%9E%E6%B4%9E%E6%9D%BF%202mm%20110x72%2084x58%20%E4%BA%9A%E5%85%8B%E5%8A%9B%E6%9D%BF</x:v>
       </x:c>
       <x:c r="G21" s="14" t="str">
-        <x:v>https://s.taobao.com/search?q=MX1.25%202P%20%E7%94%B5%E6%B1%A0%E7%BA%BF%20SH1.0%2014P%20%E8%BD%AC%E6%8E%A5%E7%BA%BF%2028AWG%20%E6%9D%9C%E9%82%A6%E7%BA%BF</x:v>
+        <x:v>https://s.taobao.com/search?q=FR4%20%E6%B4%9E%E6%B4%9E%E6%9D%BF%202mm%20110x72%2084x58%20%E4%BA%9A%E5%85%8B%E5%8A%9B%E6%9D%BF</x:v>
       </x:c>
       <x:c r="H21" s="14" t="str">
-        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=MX1.25%202P%20%E7%94%B5%E6%B1%A0%E7%BA%BF%20SH1.0%2014P%20%E8%BD%AC%E6%8E%A5%E7%BA%BF%2028AWG%20%E6%9D%9C%E9%82%A6%E7%BA%BF</x:v>
+        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=FR4%20%E6%B4%9E%E6%B4%9E%E6%9D%BF%202mm%20110x72%2084x58%20%E4%BA%9A%E5%85%8B%E5%8A%9B%E6%9D%BF</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="42" customHeight="1">
       <x:c r="A22" s="14" t="str">
-        <x:v>热缩管与绝缘材料</x:v>
+        <x:v>JST/杜邦线套装</x:v>
       </x:c>
       <x:c r="B22" s="14" t="str">
         <x:v>1 套</x:v>
@@ -860,18 +860,44 @@
         <x:v>必买</x:v>
       </x:c>
       <x:c r="D22" s="14" t="str">
+        <x:v>MX1.25 2P 电池线 SH1.0 14P 转接线 28AWG 杜邦线</x:v>
+      </x:c>
+      <x:c r="E22" s="14" t="str">
+        <x:v>主控板外露接口是小间距 SH1.0/FPC 形态，建议准备转接线或转接板；否则手工接线会很难。</x:v>
+      </x:c>
+      <x:c r="F22" s="14" t="str">
+        <x:v>https://search.jd.com/Search?keyword=MX1.25%202P%20%E7%94%B5%E6%B1%A0%E7%BA%BF%20SH1.0%2014P%20%E8%BD%AC%E6%8E%A5%E7%BA%BF%2028AWG%20%E6%9D%9C%E9%82%A6%E7%BA%BF</x:v>
+      </x:c>
+      <x:c r="G22" s="14" t="str">
+        <x:v>https://s.taobao.com/search?q=MX1.25%202P%20%E7%94%B5%E6%B1%A0%E7%BA%BF%20SH1.0%2014P%20%E8%BD%AC%E6%8E%A5%E7%BA%BF%2028AWG%20%E6%9D%9C%E9%82%A6%E7%BA%BF</x:v>
+      </x:c>
+      <x:c r="H22" s="14" t="str">
+        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=MX1.25%202P%20%E7%94%B5%E6%B1%A0%E7%BA%BF%20SH1.0%2014P%20%E8%BD%AC%E6%8E%A5%E7%BA%BF%2028AWG%20%E6%9D%9C%E9%82%A6%E7%BA%BF</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="42" customHeight="1">
+      <x:c r="A23" s="14" t="str">
+        <x:v>热缩管与绝缘材料</x:v>
+      </x:c>
+      <x:c r="B23" s="14" t="str">
+        <x:v>1 套</x:v>
+      </x:c>
+      <x:c r="C23" s="14" t="str">
+        <x:v>必买</x:v>
+      </x:c>
+      <x:c r="D23" s="14" t="str">
         <x:v>热缩管 1mm 2mm 3mm 5mm Kapton 高温胶带</x:v>
       </x:c>
-      <x:c r="E22" s="14" t="str">
+      <x:c r="E23" s="14" t="str">
         <x:v>铜架穿线处和电池引线处必须做绝缘。</x:v>
       </x:c>
-      <x:c r="F22" s="14" t="str">
+      <x:c r="F23" s="14" t="str">
         <x:v>https://search.jd.com/Search?keyword=%E7%83%AD%E7%BC%A9%E7%AE%A1%201mm%202mm%203mm%205mm%20Kapton%20%E9%AB%98%E6%B8%A9%E8%83%B6%E5%B8%A6</x:v>
       </x:c>
-      <x:c r="G22" s="14" t="str">
+      <x:c r="G23" s="14" t="str">
         <x:v>https://s.taobao.com/search?q=%E7%83%AD%E7%BC%A9%E7%AE%A1%201mm%202mm%203mm%205mm%20Kapton%20%E9%AB%98%E6%B8%A9%E8%83%B6%E5%B8%A6</x:v>
       </x:c>
-      <x:c r="H22" s="14" t="str">
+      <x:c r="H23" s="14" t="str">
         <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=%E7%83%AD%E7%BC%A9%E7%AE%A1%201mm%202mm%203mm%205mm%20Kapton%20%E9%AB%98%E6%B8%A9%E8%83%B6%E5%B8%A6</x:v>
       </x:c>
     </x:row>

--- a/Atlas_Rover_Mk1_制造图纸包_V1.0/采购执行表_Atlas_Rover_Mk1_V1.0.xlsx
+++ b/Atlas_Rover_Mk1_制造图纸包_V1.0/采购执行表_Atlas_Rover_Mk1_V1.0.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="采买执行" sheetId="1" r:id="R15b1871fc8704870"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="采买执行" sheetId="1" r:id="Rdfa99a0af6d2449b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -565,85 +565,85 @@
     </x:row>
     <x:row r="11" ht="42" customHeight="1">
       <x:c r="A11" s="14" t="str">
-        <x:v>迷你万向轮</x:v>
+        <x:v>64T 钢齿轮轮芯（备选）</x:v>
       </x:c>
       <x:c r="B11" s="14" t="str">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C11" s="14" t="str">
-        <x:v>必买</x:v>
+        <x:v>备选</x:v>
       </x:c>
       <x:c r="D11" s="14" t="str">
-        <x:v>迷你万向轮 10mm 15mm 球形 小车</x:v>
+        <x:v>64T 钢齿轮 3mm D孔 30mm 机器人 小车</x:v>
       </x:c>
       <x:c r="E11" s="14" t="str">
-        <x:v>前置万向轮能让第一版结构更简单。若底盘不水平，可加 1-2 mm 垫片。</x:v>
+        <x:v>仅在买不到合适 N20 橡胶轮时使用。钢齿轮不能默认直接套 N20，必须确认孔径/孔型；外圈建议套 O 型圈或热缩胶圈增加摩擦。</x:v>
       </x:c>
       <x:c r="F11" s="14" t="str">
-        <x:v>https://search.jd.com/Search?keyword=%E8%BF%B7%E4%BD%A0%E4%B8%87%E5%90%91%E8%BD%AE%2010mm%2015mm%20%E7%90%83%E5%BD%A2%20%E5%B0%8F%E8%BD%A6</x:v>
+        <x:v>https://search.jd.com/Search?keyword=64T%20%E9%92%A2%E9%BD%BF%E8%BD%AE%203mm%20D%E5%AD%94%2030mm%20%E6%9C%BA%E5%99%A8%E4%BA%BA%20%E5%B0%8F%E8%BD%A6</x:v>
       </x:c>
       <x:c r="G11" s="14" t="str">
-        <x:v>https://s.taobao.com/search?q=%E8%BF%B7%E4%BD%A0%E4%B8%87%E5%90%91%E8%BD%AE%2010mm%2015mm%20%E7%90%83%E5%BD%A2%20%E5%B0%8F%E8%BD%A6</x:v>
+        <x:v>https://s.taobao.com/search?q=64T%20%E9%92%A2%E9%BD%BF%E8%BD%AE%203mm%20D%E5%AD%94%2030mm%20%E6%9C%BA%E5%99%A8%E4%BA%BA%20%E5%B0%8F%E8%BD%A6</x:v>
       </x:c>
       <x:c r="H11" s="14" t="str">
-        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=%E8%BF%B7%E4%BD%A0%E4%B8%87%E5%90%91%E8%BD%AE%2010mm%2015mm%20%E7%90%83%E5%BD%A2%20%E5%B0%8F%E8%BD%A6</x:v>
+        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=64T%20%E9%92%A2%E9%BD%BF%E8%BD%AE%203mm%20D%E5%AD%94%2030mm%20%E6%9C%BA%E5%99%A8%E4%BA%BA%20%E5%B0%8F%E8%BD%A6</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="42" customHeight="1">
       <x:c r="A12" s="14" t="str">
-        <x:v>18650 锂电池</x:v>
+        <x:v>3 mm D 孔轮毂或夹紧适配器</x:v>
       </x:c>
       <x:c r="B12" s="14" t="str">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C12" s="14" t="str">
-        <x:v>必买</x:v>
+        <x:v>备选</x:v>
       </x:c>
       <x:c r="D12" s="14" t="str">
-        <x:v>18650 锂电池 3.7V 2600mAh 带保护板 持续放电3A</x:v>
+        <x:v>3mm D孔 轮毂 N20 电机 联轴器 M2 固定</x:v>
       </x:c>
       <x:c r="E12" s="14" t="str">
-        <x:v>裸电芯约 18 x 65 mm；带保护板或尖头电芯可能更长。避免虚标容量电池，电机启动电流会拉低电压。</x:v>
+        <x:v>64T 齿轮若不是 3 mm D 孔直连，必须用轮毂/夹片转接；不建议只用胶水粘。</x:v>
       </x:c>
       <x:c r="F12" s="14" t="str">
-        <x:v>https://search.jd.com/Search?keyword=18650%20%E9%94%82%E7%94%B5%E6%B1%A0%203.7V%202600mAh%20%E5%B8%A6%E4%BF%9D%E6%8A%A4%E6%9D%BF%20%E6%8C%81%E7%BB%AD%E6%94%BE%E7%94%B53A</x:v>
+        <x:v>https://search.jd.com/Search?keyword=3mm%20D%E5%AD%94%20%E8%BD%AE%E6%AF%82%20N20%20%E7%94%B5%E6%9C%BA%20%E8%81%94%E8%BD%B4%E5%99%A8%20M2%20%E5%9B%BA%E5%AE%9A</x:v>
       </x:c>
       <x:c r="G12" s="14" t="str">
-        <x:v>https://s.taobao.com/search?q=18650%20%E9%94%82%E7%94%B5%E6%B1%A0%203.7V%202600mAh%20%E5%B8%A6%E4%BF%9D%E6%8A%A4%E6%9D%BF%20%E6%8C%81%E7%BB%AD%E6%94%BE%E7%94%B53A</x:v>
+        <x:v>https://s.taobao.com/search?q=3mm%20D%E5%AD%94%20%E8%BD%AE%E6%AF%82%20N20%20%E7%94%B5%E6%9C%BA%20%E8%81%94%E8%BD%B4%E5%99%A8%20M2%20%E5%9B%BA%E5%AE%9A</x:v>
       </x:c>
       <x:c r="H12" s="14" t="str">
-        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=18650%20%E9%94%82%E7%94%B5%E6%B1%A0%203.7V%202600mAh%20%E5%B8%A6%E4%BF%9D%E6%8A%A4%E6%9D%BF%20%E6%8C%81%E7%BB%AD%E6%94%BE%E7%94%B53A</x:v>
+        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=3mm%20D%E5%AD%94%20%E8%BD%AE%E6%AF%82%20N20%20%E7%94%B5%E6%9C%BA%20%E8%81%94%E8%BD%B4%E5%99%A8%20M2%20%E5%9B%BA%E5%AE%9A</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="42" customHeight="1">
       <x:c r="A13" s="14" t="str">
-        <x:v>单节 18650 电池盒带线</x:v>
+        <x:v>齿轮外圈防滑圈</x:v>
       </x:c>
       <x:c r="B13" s="14" t="str">
-        <x:v>1</x:v>
+        <x:v>2-4</x:v>
       </x:c>
       <x:c r="C13" s="14" t="str">
-        <x:v>必买</x:v>
+        <x:v>备选</x:v>
       </x:c>
       <x:c r="D13" s="14" t="str">
-        <x:v>单节 18650 电池盒 带线 1节</x:v>
+        <x:v>橡胶 O型圈 热缩管 30mm 35mm 轮胎 防滑</x:v>
       </x:c>
       <x:c r="E13" s="14" t="str">
-        <x:v>沿底层长度方向安装。双节电池盒不属于 Mk.1 方案。</x:v>
+        <x:v>钢齿轮直接接触桌面会滑、响、伤桌面；外圈必须加橡胶圈或热缩圈。</x:v>
       </x:c>
       <x:c r="F13" s="14" t="str">
-        <x:v>https://search.jd.com/Search?keyword=%E5%8D%95%E8%8A%82%2018650%20%E7%94%B5%E6%B1%A0%E7%9B%92%20%E5%B8%A6%E7%BA%BF%201%E8%8A%82</x:v>
+        <x:v>https://search.jd.com/Search?keyword=%E6%A9%A1%E8%83%B6%20O%E5%9E%8B%E5%9C%88%20%E7%83%AD%E7%BC%A9%E7%AE%A1%2030mm%2035mm%20%E8%BD%AE%E8%83%8E%20%E9%98%B2%E6%BB%91</x:v>
       </x:c>
       <x:c r="G13" s="14" t="str">
-        <x:v>https://s.taobao.com/search?q=%E5%8D%95%E8%8A%82%2018650%20%E7%94%B5%E6%B1%A0%E7%9B%92%20%E5%B8%A6%E7%BA%BF%201%E8%8A%82</x:v>
+        <x:v>https://s.taobao.com/search?q=%E6%A9%A1%E8%83%B6%20O%E5%9E%8B%E5%9C%88%20%E7%83%AD%E7%BC%A9%E7%AE%A1%2030mm%2035mm%20%E8%BD%AE%E8%83%8E%20%E9%98%B2%E6%BB%91</x:v>
       </x:c>
       <x:c r="H13" s="14" t="str">
-        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=%E5%8D%95%E8%8A%82%2018650%20%E7%94%B5%E6%B1%A0%E7%9B%92%20%E5%B8%A6%E7%BA%BF%201%E8%8A%82</x:v>
+        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=%E6%A9%A1%E8%83%B6%20O%E5%9E%8B%E5%9C%88%20%E7%83%AD%E7%BC%A9%E7%AE%A1%2030mm%2035mm%20%E8%BD%AE%E8%83%8E%20%E9%98%B2%E6%BB%91</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="42" customHeight="1">
       <x:c r="A14" s="14" t="str">
-        <x:v>5 V 升压模块</x:v>
+        <x:v>迷你万向轮</x:v>
       </x:c>
       <x:c r="B14" s="14" t="str">
         <x:v>1</x:v>
@@ -652,206 +652,206 @@
         <x:v>必买</x:v>
       </x:c>
       <x:c r="D14" s="14" t="str">
-        <x:v>锂电池升压模块 3.7V转5V 2A 3A</x:v>
+        <x:v>迷你万向轮 10mm 15mm 球形 小车</x:v>
       </x:c>
       <x:c r="E14" s="14" t="str">
-        <x:v>只给电机支路使用。不要让电机电流经过 ESP32 的 3.3 V 电源轨。若两个 N20 堵转明显，优先换更大电流模块。</x:v>
+        <x:v>前置万向轮能让第一版结构更简单。若底盘不水平，可加 1-2 mm 垫片。</x:v>
       </x:c>
       <x:c r="F14" s="14" t="str">
-        <x:v>https://search.jd.com/Search?keyword=%E9%94%82%E7%94%B5%E6%B1%A0%E5%8D%87%E5%8E%8B%E6%A8%A1%E5%9D%97%203.7V%E8%BD%AC5V%202A%203A</x:v>
+        <x:v>https://search.jd.com/Search?keyword=%E8%BF%B7%E4%BD%A0%E4%B8%87%E5%90%91%E8%BD%AE%2010mm%2015mm%20%E7%90%83%E5%BD%A2%20%E5%B0%8F%E8%BD%A6</x:v>
       </x:c>
       <x:c r="G14" s="14" t="str">
-        <x:v>https://s.taobao.com/search?q=%E9%94%82%E7%94%B5%E6%B1%A0%E5%8D%87%E5%8E%8B%E6%A8%A1%E5%9D%97%203.7V%E8%BD%AC5V%202A%203A</x:v>
+        <x:v>https://s.taobao.com/search?q=%E8%BF%B7%E4%BD%A0%E4%B8%87%E5%90%91%E8%BD%AE%2010mm%2015mm%20%E7%90%83%E5%BD%A2%20%E5%B0%8F%E8%BD%A6</x:v>
       </x:c>
       <x:c r="H14" s="14" t="str">
-        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=%E9%94%82%E7%94%B5%E6%B1%A0%E5%8D%87%E5%8E%8B%E6%A8%A1%E5%9D%97%203.7V%E8%BD%AC5V%202A%203A</x:v>
+        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=%E8%BF%B7%E4%BD%A0%E4%B8%87%E5%90%91%E8%BD%AE%2010mm%2015mm%20%E7%90%83%E5%BD%A2%20%E5%B0%8F%E8%BD%A6</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="42" customHeight="1">
       <x:c r="A15" s="14" t="str">
-        <x:v>电源开关与保护</x:v>
+        <x:v>18650 锂电池</x:v>
       </x:c>
       <x:c r="B15" s="14" t="str">
-        <x:v>1 套</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C15" s="14" t="str">
         <x:v>必买</x:v>
       </x:c>
       <x:c r="D15" s="14" t="str">
-        <x:v>迷你拨动开关 1S 18650 保护板 3.7V</x:v>
+        <x:v>18650 锂电池 3.7V 2600mAh 带保护板 持续放电3A</x:v>
       </x:c>
       <x:c r="E15" s="14" t="str">
-        <x:v>只保留一条充电路径。除非电池路径隔离，不要把 TP4056 与板载充电并联。</x:v>
+        <x:v>裸电芯约 18 x 65 mm；带保护板或尖头电芯可能更长。避免虚标容量电池，电机启动电流会拉低电压。</x:v>
       </x:c>
       <x:c r="F15" s="14" t="str">
-        <x:v>https://search.jd.com/Search?keyword=%E8%BF%B7%E4%BD%A0%E6%8B%A8%E5%8A%A8%E5%BC%80%E5%85%B3%201S%2018650%20%E4%BF%9D%E6%8A%A4%E6%9D%BF%203.7V</x:v>
+        <x:v>https://search.jd.com/Search?keyword=18650%20%E9%94%82%E7%94%B5%E6%B1%A0%203.7V%202600mAh%20%E5%B8%A6%E4%BF%9D%E6%8A%A4%E6%9D%BF%20%E6%8C%81%E7%BB%AD%E6%94%BE%E7%94%B53A</x:v>
       </x:c>
       <x:c r="G15" s="14" t="str">
-        <x:v>https://s.taobao.com/search?q=%E8%BF%B7%E4%BD%A0%E6%8B%A8%E5%8A%A8%E5%BC%80%E5%85%B3%201S%2018650%20%E4%BF%9D%E6%8A%A4%E6%9D%BF%203.7V</x:v>
+        <x:v>https://s.taobao.com/search?q=18650%20%E9%94%82%E7%94%B5%E6%B1%A0%203.7V%202600mAh%20%E5%B8%A6%E4%BF%9D%E6%8A%A4%E6%9D%BF%20%E6%8C%81%E7%BB%AD%E6%94%BE%E7%94%B53A</x:v>
       </x:c>
       <x:c r="H15" s="14" t="str">
-        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=%E8%BF%B7%E4%BD%A0%E6%8B%A8%E5%8A%A8%E5%BC%80%E5%85%B3%201S%2018650%20%E4%BF%9D%E6%8A%A4%E6%9D%BF%203.7V</x:v>
+        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=18650%20%E9%94%82%E7%94%B5%E6%B1%A0%203.7V%202600mAh%20%E5%B8%A6%E4%BF%9D%E6%8A%A4%E6%9D%BF%20%E6%8C%81%E7%BB%AD%E6%94%BE%E7%94%B53A</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="42" customHeight="1">
       <x:c r="A16" s="14" t="str">
-        <x:v>小喇叭</x:v>
+        <x:v>单节 18650 电池盒带线</x:v>
       </x:c>
       <x:c r="B16" s="14" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C16" s="14" t="str">
-        <x:v>推荐</x:v>
+        <x:v>必买</x:v>
       </x:c>
       <x:c r="D16" s="14" t="str">
-        <x:v>4欧3W 小喇叭 直径40mm 以下</x:v>
+        <x:v>单节 18650 电池盒 带线 1节</x:v>
       </x:c>
       <x:c r="E16" s="14" t="str">
-        <x:v>主控板已有麦克风、音频编解码、功放和喇叭接口；但通常仍需外接一个小喇叭才能外放。Mk.1 不必购买 MAX98357A 和 INMP441。</x:v>
+        <x:v>沿底层长度方向安装。双节电池盒不属于 Mk.1 方案。</x:v>
       </x:c>
       <x:c r="F16" s="14" t="str">
-        <x:v>https://search.jd.com/Search?keyword=4%E6%AC%A73W%20%E5%B0%8F%E5%96%87%E5%8F%AD%20%E7%9B%B4%E5%BE%8440mm%20%E4%BB%A5%E4%B8%8B</x:v>
+        <x:v>https://search.jd.com/Search?keyword=%E5%8D%95%E8%8A%82%2018650%20%E7%94%B5%E6%B1%A0%E7%9B%92%20%E5%B8%A6%E7%BA%BF%201%E8%8A%82</x:v>
       </x:c>
       <x:c r="G16" s="14" t="str">
-        <x:v>https://s.taobao.com/search?q=4%E6%AC%A73W%20%E5%B0%8F%E5%96%87%E5%8F%AD%20%E7%9B%B4%E5%BE%8440mm%20%E4%BB%A5%E4%B8%8B</x:v>
+        <x:v>https://s.taobao.com/search?q=%E5%8D%95%E8%8A%82%2018650%20%E7%94%B5%E6%B1%A0%E7%9B%92%20%E5%B8%A6%E7%BA%BF%201%E8%8A%82</x:v>
       </x:c>
       <x:c r="H16" s="14" t="str">
-        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=4%E6%AC%A73W%20%E5%B0%8F%E5%96%87%E5%8F%AD%20%E7%9B%B4%E5%BE%8440mm%20%E4%BB%A5%E4%B8%8B</x:v>
+        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=%E5%8D%95%E8%8A%82%2018650%20%E7%94%B5%E6%B1%A0%E7%9B%92%20%E5%B8%A6%E7%BA%BF%201%E8%8A%82</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="42" customHeight="1">
       <x:c r="A17" s="14" t="str">
-        <x:v>WS2812B 灯条或灯环（外接车灯模块）</x:v>
+        <x:v>5 V 升压模块</x:v>
       </x:c>
       <x:c r="B17" s="14" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C17" s="14" t="str">
-        <x:v>推荐</x:v>
+        <x:v>必买</x:v>
       </x:c>
       <x:c r="D17" s="14" t="str">
-        <x:v>WS2812B 8位 灯环 5V 30mm</x:v>
+        <x:v>锂电池升压模块 3.7V转5V 2A 3A</x:v>
       </x:c>
       <x:c r="E17" s="14" t="str">
-        <x:v>这就是解决“没有集成车灯/RGB”的外接灯光模块。需要 5 V、GND 和 1 个数据 GPIO；8 颗灯全白约 0.48 A，建议限亮度并加 330 欧数据电阻和 470-1000 uF 电容。</x:v>
+        <x:v>只给电机支路使用。不要让电机电流经过 ESP32 的 3.3 V 电源轨。若两个 N20 堵转明显，优先换更大电流模块。</x:v>
       </x:c>
       <x:c r="F17" s="14" t="str">
-        <x:v>https://search.jd.com/Search?keyword=WS2812B%208%E4%BD%8D%20%E7%81%AF%E7%8E%AF%205V%2030mm</x:v>
+        <x:v>https://search.jd.com/Search?keyword=%E9%94%82%E7%94%B5%E6%B1%A0%E5%8D%87%E5%8E%8B%E6%A8%A1%E5%9D%97%203.7V%E8%BD%AC5V%202A%203A</x:v>
       </x:c>
       <x:c r="G17" s="14" t="str">
-        <x:v>https://s.taobao.com/search?q=WS2812B%208%E4%BD%8D%20%E7%81%AF%E7%8E%AF%205V%2030mm</x:v>
+        <x:v>https://s.taobao.com/search?q=%E9%94%82%E7%94%B5%E6%B1%A0%E5%8D%87%E5%8E%8B%E6%A8%A1%E5%9D%97%203.7V%E8%BD%AC5V%202A%203A</x:v>
       </x:c>
       <x:c r="H17" s="14" t="str">
-        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=WS2812B%208%E4%BD%8D%20%E7%81%AF%E7%8E%AF%205V%2030mm</x:v>
+        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=%E9%94%82%E7%94%B5%E6%B1%A0%E5%8D%87%E5%8E%8B%E6%A8%A1%E5%9D%97%203.7V%E8%BD%AC5V%202A%203A</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="42" customHeight="1">
       <x:c r="A18" s="14" t="str">
-        <x:v>WS2812B 数据电平转换器（推荐）</x:v>
+        <x:v>电源开关与保护</x:v>
       </x:c>
       <x:c r="B18" s="14" t="str">
-        <x:v>1</x:v>
+        <x:v>1 套</x:v>
       </x:c>
       <x:c r="C18" s="14" t="str">
-        <x:v>推荐</x:v>
+        <x:v>必买</x:v>
       </x:c>
       <x:c r="D18" s="14" t="str">
-        <x:v>SN74AHCT1G125 74AHCT125 74HCT14 3.3V转5V 电平转换</x:v>
+        <x:v>迷你拨动开关 1S 18650 保护板 3.7V</x:v>
       </x:c>
       <x:c r="E18" s="14" t="str">
-        <x:v>WS2812B 用 5 V 供电时，数据高电平按规格需要接近 3.5 V；ESP32 的 3.3 V 短线常能跑，但不够稳。推荐用 AHCT/HCT 电平转换：A 接 ESP32 数据 GPIO，Y 经 330 欧到 DIN，芯片 VCC 接 5 V，GND 共地。</x:v>
+        <x:v>只保留一条充电路径。除非电池路径隔离，不要把 TP4056 与板载充电并联。</x:v>
       </x:c>
       <x:c r="F18" s="14" t="str">
-        <x:v>https://search.jd.com/Search?keyword=SN74AHCT1G125%2074AHCT125%2074HCT14%203.3V%E8%BD%AC5V%20%E7%94%B5%E5%B9%B3%E8%BD%AC%E6%8D%A2</x:v>
+        <x:v>https://search.jd.com/Search?keyword=%E8%BF%B7%E4%BD%A0%E6%8B%A8%E5%8A%A8%E5%BC%80%E5%85%B3%201S%2018650%20%E4%BF%9D%E6%8A%A4%E6%9D%BF%203.7V</x:v>
       </x:c>
       <x:c r="G18" s="14" t="str">
-        <x:v>https://s.taobao.com/search?q=SN74AHCT1G125%2074AHCT125%2074HCT14%203.3V%E8%BD%AC5V%20%E7%94%B5%E5%B9%B3%E8%BD%AC%E6%8D%A2</x:v>
+        <x:v>https://s.taobao.com/search?q=%E8%BF%B7%E4%BD%A0%E6%8B%A8%E5%8A%A8%E5%BC%80%E5%85%B3%201S%2018650%20%E4%BF%9D%E6%8A%A4%E6%9D%BF%203.7V</x:v>
       </x:c>
       <x:c r="H18" s="14" t="str">
-        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=SN74AHCT1G125%2074AHCT125%2074HCT14%203.3V%E8%BD%AC5V%20%E7%94%B5%E5%B9%B3%E8%BD%AC%E6%8D%A2</x:v>
+        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=%E8%BF%B7%E4%BD%A0%E6%8B%A8%E5%8A%A8%E5%BC%80%E5%85%B3%201S%2018650%20%E4%BF%9D%E6%8A%A4%E6%9D%BF%203.7V</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="42" customHeight="1">
       <x:c r="A19" s="14" t="str">
-        <x:v>黄铜丝/黄铜棒</x:v>
+        <x:v>小喇叭</x:v>
       </x:c>
       <x:c r="B19" s="14" t="str">
-        <x:v>1 套</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C19" s="14" t="str">
-        <x:v>必买</x:v>
+        <x:v>推荐</x:v>
       </x:c>
       <x:c r="D19" s="14" t="str">
-        <x:v>黄铜棒 2mm 3米 1.5mm 2米 1mm 黄铜丝 模型 DIY</x:v>
+        <x:v>4欧3W 小喇叭 直径40mm 以下</x:v>
       </x:c>
       <x:c r="E19" s="14" t="str">
-        <x:v>2.0 mm 做底框、护栏、立柱和顶部提手；1.5 mm 做护眼圈、斜撑和灯架；1.0 mm 只用于绑扎焊点或装饰，不承担主结构。焊接前预上锡，铜架必须与带电焊盘绝缘。</x:v>
+        <x:v>主控板已有麦克风、音频编解码、功放和喇叭接口；但通常仍需外接一个小喇叭才能外放。Mk.1 不必购买 MAX98357A 和 INMP441。</x:v>
       </x:c>
       <x:c r="F19" s="14" t="str">
-        <x:v>https://search.jd.com/Search?keyword=%E9%BB%84%E9%93%9C%E6%A3%92%202mm%203%E7%B1%B3%201.5mm%202%E7%B1%B3%201mm%20%E9%BB%84%E9%93%9C%E4%B8%9D%20%E6%A8%A1%E5%9E%8B%20DIY</x:v>
+        <x:v>https://search.jd.com/Search?keyword=4%E6%AC%A73W%20%E5%B0%8F%E5%96%87%E5%8F%AD%20%E7%9B%B4%E5%BE%8440mm%20%E4%BB%A5%E4%B8%8B</x:v>
       </x:c>
       <x:c r="G19" s="14" t="str">
-        <x:v>https://s.taobao.com/search?q=%E9%BB%84%E9%93%9C%E6%A3%92%202mm%203%E7%B1%B3%201.5mm%202%E7%B1%B3%201mm%20%E9%BB%84%E9%93%9C%E4%B8%9D%20%E6%A8%A1%E5%9E%8B%20DIY</x:v>
+        <x:v>https://s.taobao.com/search?q=4%E6%AC%A73W%20%E5%B0%8F%E5%96%87%E5%8F%AD%20%E7%9B%B4%E5%BE%8440mm%20%E4%BB%A5%E4%B8%8B</x:v>
       </x:c>
       <x:c r="H19" s="14" t="str">
-        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=%E9%BB%84%E9%93%9C%E6%A3%92%202mm%203%E7%B1%B3%201.5mm%202%E7%B1%B3%201mm%20%E9%BB%84%E9%93%9C%E4%B8%9D%20%E6%A8%A1%E5%9E%8B%20DIY</x:v>
+        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=4%E6%AC%A73W%20%E5%B0%8F%E5%96%87%E5%8F%AD%20%E7%9B%B4%E5%BE%8440mm%20%E4%BB%A5%E4%B8%8B</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="42" customHeight="1">
       <x:c r="A20" s="14" t="str">
-        <x:v>M2 铜柱套装</x:v>
+        <x:v>WS2812B 灯条或灯环（外接车灯模块）</x:v>
       </x:c>
       <x:c r="B20" s="14" t="str">
-        <x:v>1 套</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C20" s="14" t="str">
-        <x:v>必买</x:v>
+        <x:v>推荐</x:v>
       </x:c>
       <x:c r="D20" s="14" t="str">
-        <x:v>M2 铜柱套装 双通 6 8 10 12 15 20mm 螺丝</x:v>
+        <x:v>WS2812B 8位 灯环 5V 30mm</x:v>
       </x:c>
       <x:c r="E20" s="14" t="str">
-        <x:v>用 M2，不用 M3。双眼主控板官方安装孔为 M2。</x:v>
+        <x:v>这就是解决“没有集成车灯/RGB”的外接灯光模块。需要 5 V、GND 和 1 个数据 GPIO；8 颗灯全白约 0.48 A，建议限亮度并加 330 欧数据电阻和 470-1000 uF 电容。</x:v>
       </x:c>
       <x:c r="F20" s="14" t="str">
-        <x:v>https://search.jd.com/Search?keyword=M2%20%E9%93%9C%E6%9F%B1%E5%A5%97%E8%A3%85%20%E5%8F%8C%E9%80%9A%206%208%2010%2012%2015%2020mm%20%E8%9E%BA%E4%B8%9D</x:v>
+        <x:v>https://search.jd.com/Search?keyword=WS2812B%208%E4%BD%8D%20%E7%81%AF%E7%8E%AF%205V%2030mm</x:v>
       </x:c>
       <x:c r="G20" s="14" t="str">
-        <x:v>https://s.taobao.com/search?q=M2%20%E9%93%9C%E6%9F%B1%E5%A5%97%E8%A3%85%20%E5%8F%8C%E9%80%9A%206%208%2010%2012%2015%2020mm%20%E8%9E%BA%E4%B8%9D</x:v>
+        <x:v>https://s.taobao.com/search?q=WS2812B%208%E4%BD%8D%20%E7%81%AF%E7%8E%AF%205V%2030mm</x:v>
       </x:c>
       <x:c r="H20" s="14" t="str">
-        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=M2%20%E9%93%9C%E6%9F%B1%E5%A5%97%E8%A3%85%20%E5%8F%8C%E9%80%9A%206%208%2010%2012%2015%2020mm%20%E8%9E%BA%E4%B8%9D</x:v>
+        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=WS2812B%208%E4%BD%8D%20%E7%81%AF%E7%8E%AF%205V%2030mm</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="42" customHeight="1">
       <x:c r="A21" s="14" t="str">
-        <x:v>层板材料</x:v>
+        <x:v>WS2812B 数据电平转换器（推荐）</x:v>
       </x:c>
       <x:c r="B21" s="14" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C21" s="14" t="str">
-        <x:v>必买</x:v>
+        <x:v>推荐</x:v>
       </x:c>
       <x:c r="D21" s="14" t="str">
-        <x:v>FR4 洞洞板 2mm 110x72 84x58 亚克力板</x:v>
+        <x:v>SN74AHCT1G125 74AHCT125 74HCT14 3.3V转5V 电平转换</x:v>
       </x:c>
       <x:c r="E21" s="14" t="str">
-        <x:v>FR4 洞洞板更适合手工钻孔；亚克力更好看，但加工过急容易裂。</x:v>
+        <x:v>WS2812B 用 5 V 供电时，数据高电平按规格需要接近 3.5 V；ESP32 的 3.3 V 短线常能跑，但不够稳。推荐用 AHCT/HCT 电平转换：A 接 ESP32 数据 GPIO，Y 经 330 欧到 DIN，芯片 VCC 接 5 V，GND 共地。</x:v>
       </x:c>
       <x:c r="F21" s="14" t="str">
-        <x:v>https://search.jd.com/Search?keyword=FR4%20%E6%B4%9E%E6%B4%9E%E6%9D%BF%202mm%20110x72%2084x58%20%E4%BA%9A%E5%85%8B%E5%8A%9B%E6%9D%BF</x:v>
+        <x:v>https://search.jd.com/Search?keyword=SN74AHCT1G125%2074AHCT125%2074HCT14%203.3V%E8%BD%AC5V%20%E7%94%B5%E5%B9%B3%E8%BD%AC%E6%8D%A2</x:v>
       </x:c>
       <x:c r="G21" s="14" t="str">
-        <x:v>https://s.taobao.com/search?q=FR4%20%E6%B4%9E%E6%B4%9E%E6%9D%BF%202mm%20110x72%2084x58%20%E4%BA%9A%E5%85%8B%E5%8A%9B%E6%9D%BF</x:v>
+        <x:v>https://s.taobao.com/search?q=SN74AHCT1G125%2074AHCT125%2074HCT14%203.3V%E8%BD%AC5V%20%E7%94%B5%E5%B9%B3%E8%BD%AC%E6%8D%A2</x:v>
       </x:c>
       <x:c r="H21" s="14" t="str">
-        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=FR4%20%E6%B4%9E%E6%B4%9E%E6%9D%BF%202mm%20110x72%2084x58%20%E4%BA%9A%E5%85%8B%E5%8A%9B%E6%9D%BF</x:v>
+        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=SN74AHCT1G125%2074AHCT125%2074HCT14%203.3V%E8%BD%AC5V%20%E7%94%B5%E5%B9%B3%E8%BD%AC%E6%8D%A2</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="42" customHeight="1">
       <x:c r="A22" s="14" t="str">
-        <x:v>JST/杜邦线套装</x:v>
+        <x:v>黄铜丝/黄铜棒</x:v>
       </x:c>
       <x:c r="B22" s="14" t="str">
         <x:v>1 套</x:v>
@@ -860,24 +860,24 @@
         <x:v>必买</x:v>
       </x:c>
       <x:c r="D22" s="14" t="str">
-        <x:v>MX1.25 2P 电池线 SH1.0 14P 转接线 28AWG 杜邦线</x:v>
+        <x:v>黄铜棒 2mm 3米 1.5mm 2米 1mm 黄铜丝 模型 DIY</x:v>
       </x:c>
       <x:c r="E22" s="14" t="str">
-        <x:v>主控板外露接口是小间距 SH1.0/FPC 形态，建议准备转接线或转接板；否则手工接线会很难。</x:v>
+        <x:v>2.0 mm 做底框、护栏、立柱和顶部提手；1.5 mm 做护眼圈、斜撑和灯架；1.0 mm 只用于绑扎焊点或装饰，不承担主结构。焊接前预上锡，铜架必须与带电焊盘绝缘。</x:v>
       </x:c>
       <x:c r="F22" s="14" t="str">
-        <x:v>https://search.jd.com/Search?keyword=MX1.25%202P%20%E7%94%B5%E6%B1%A0%E7%BA%BF%20SH1.0%2014P%20%E8%BD%AC%E6%8E%A5%E7%BA%BF%2028AWG%20%E6%9D%9C%E9%82%A6%E7%BA%BF</x:v>
+        <x:v>https://search.jd.com/Search?keyword=%E9%BB%84%E9%93%9C%E6%A3%92%202mm%203%E7%B1%B3%201.5mm%202%E7%B1%B3%201mm%20%E9%BB%84%E9%93%9C%E4%B8%9D%20%E6%A8%A1%E5%9E%8B%20DIY</x:v>
       </x:c>
       <x:c r="G22" s="14" t="str">
-        <x:v>https://s.taobao.com/search?q=MX1.25%202P%20%E7%94%B5%E6%B1%A0%E7%BA%BF%20SH1.0%2014P%20%E8%BD%AC%E6%8E%A5%E7%BA%BF%2028AWG%20%E6%9D%9C%E9%82%A6%E7%BA%BF</x:v>
+        <x:v>https://s.taobao.com/search?q=%E9%BB%84%E9%93%9C%E6%A3%92%202mm%203%E7%B1%B3%201.5mm%202%E7%B1%B3%201mm%20%E9%BB%84%E9%93%9C%E4%B8%9D%20%E6%A8%A1%E5%9E%8B%20DIY</x:v>
       </x:c>
       <x:c r="H22" s="14" t="str">
-        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=MX1.25%202P%20%E7%94%B5%E6%B1%A0%E7%BA%BF%20SH1.0%2014P%20%E8%BD%AC%E6%8E%A5%E7%BA%BF%2028AWG%20%E6%9D%9C%E9%82%A6%E7%BA%BF</x:v>
+        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=%E9%BB%84%E9%93%9C%E6%A3%92%202mm%203%E7%B1%B3%201.5mm%202%E7%B1%B3%201mm%20%E9%BB%84%E9%93%9C%E4%B8%9D%20%E6%A8%A1%E5%9E%8B%20DIY</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="42" customHeight="1">
       <x:c r="A23" s="14" t="str">
-        <x:v>热缩管与绝缘材料</x:v>
+        <x:v>M2 铜柱套装</x:v>
       </x:c>
       <x:c r="B23" s="14" t="str">
         <x:v>1 套</x:v>
@@ -886,18 +886,96 @@
         <x:v>必买</x:v>
       </x:c>
       <x:c r="D23" s="14" t="str">
+        <x:v>M2 铜柱套装 双通 6 8 10 12 15 20mm 螺丝</x:v>
+      </x:c>
+      <x:c r="E23" s="14" t="str">
+        <x:v>用 M2，不用 M3。双眼主控板官方安装孔为 M2。</x:v>
+      </x:c>
+      <x:c r="F23" s="14" t="str">
+        <x:v>https://search.jd.com/Search?keyword=M2%20%E9%93%9C%E6%9F%B1%E5%A5%97%E8%A3%85%20%E5%8F%8C%E9%80%9A%206%208%2010%2012%2015%2020mm%20%E8%9E%BA%E4%B8%9D</x:v>
+      </x:c>
+      <x:c r="G23" s="14" t="str">
+        <x:v>https://s.taobao.com/search?q=M2%20%E9%93%9C%E6%9F%B1%E5%A5%97%E8%A3%85%20%E5%8F%8C%E9%80%9A%206%208%2010%2012%2015%2020mm%20%E8%9E%BA%E4%B8%9D</x:v>
+      </x:c>
+      <x:c r="H23" s="14" t="str">
+        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=M2%20%E9%93%9C%E6%9F%B1%E5%A5%97%E8%A3%85%20%E5%8F%8C%E9%80%9A%206%208%2010%2012%2015%2020mm%20%E8%9E%BA%E4%B8%9D</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="42" customHeight="1">
+      <x:c r="A24" s="14" t="str">
+        <x:v>层板材料</x:v>
+      </x:c>
+      <x:c r="B24" s="14" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C24" s="14" t="str">
+        <x:v>必买</x:v>
+      </x:c>
+      <x:c r="D24" s="14" t="str">
+        <x:v>FR4 洞洞板 2mm 110x72 84x58 亚克力板</x:v>
+      </x:c>
+      <x:c r="E24" s="14" t="str">
+        <x:v>FR4 洞洞板更适合手工钻孔；亚克力更好看，但加工过急容易裂。</x:v>
+      </x:c>
+      <x:c r="F24" s="14" t="str">
+        <x:v>https://search.jd.com/Search?keyword=FR4%20%E6%B4%9E%E6%B4%9E%E6%9D%BF%202mm%20110x72%2084x58%20%E4%BA%9A%E5%85%8B%E5%8A%9B%E6%9D%BF</x:v>
+      </x:c>
+      <x:c r="G24" s="14" t="str">
+        <x:v>https://s.taobao.com/search?q=FR4%20%E6%B4%9E%E6%B4%9E%E6%9D%BF%202mm%20110x72%2084x58%20%E4%BA%9A%E5%85%8B%E5%8A%9B%E6%9D%BF</x:v>
+      </x:c>
+      <x:c r="H24" s="14" t="str">
+        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=FR4%20%E6%B4%9E%E6%B4%9E%E6%9D%BF%202mm%20110x72%2084x58%20%E4%BA%9A%E5%85%8B%E5%8A%9B%E6%9D%BF</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="42" customHeight="1">
+      <x:c r="A25" s="14" t="str">
+        <x:v>JST/杜邦线套装</x:v>
+      </x:c>
+      <x:c r="B25" s="14" t="str">
+        <x:v>1 套</x:v>
+      </x:c>
+      <x:c r="C25" s="14" t="str">
+        <x:v>必买</x:v>
+      </x:c>
+      <x:c r="D25" s="14" t="str">
+        <x:v>MX1.25 2P 电池线 SH1.0 14P 转接线 28AWG 杜邦线</x:v>
+      </x:c>
+      <x:c r="E25" s="14" t="str">
+        <x:v>主控板外露接口是小间距 SH1.0/FPC 形态，建议准备转接线或转接板；否则手工接线会很难。</x:v>
+      </x:c>
+      <x:c r="F25" s="14" t="str">
+        <x:v>https://search.jd.com/Search?keyword=MX1.25%202P%20%E7%94%B5%E6%B1%A0%E7%BA%BF%20SH1.0%2014P%20%E8%BD%AC%E6%8E%A5%E7%BA%BF%2028AWG%20%E6%9D%9C%E9%82%A6%E7%BA%BF</x:v>
+      </x:c>
+      <x:c r="G25" s="14" t="str">
+        <x:v>https://s.taobao.com/search?q=MX1.25%202P%20%E7%94%B5%E6%B1%A0%E7%BA%BF%20SH1.0%2014P%20%E8%BD%AC%E6%8E%A5%E7%BA%BF%2028AWG%20%E6%9D%9C%E9%82%A6%E7%BA%BF</x:v>
+      </x:c>
+      <x:c r="H25" s="14" t="str">
+        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=MX1.25%202P%20%E7%94%B5%E6%B1%A0%E7%BA%BF%20SH1.0%2014P%20%E8%BD%AC%E6%8E%A5%E7%BA%BF%2028AWG%20%E6%9D%9C%E9%82%A6%E7%BA%BF</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="42" customHeight="1">
+      <x:c r="A26" s="14" t="str">
+        <x:v>热缩管与绝缘材料</x:v>
+      </x:c>
+      <x:c r="B26" s="14" t="str">
+        <x:v>1 套</x:v>
+      </x:c>
+      <x:c r="C26" s="14" t="str">
+        <x:v>必买</x:v>
+      </x:c>
+      <x:c r="D26" s="14" t="str">
         <x:v>热缩管 1mm 2mm 3mm 5mm Kapton 高温胶带</x:v>
       </x:c>
-      <x:c r="E23" s="14" t="str">
+      <x:c r="E26" s="14" t="str">
         <x:v>铜架穿线处和电池引线处必须做绝缘。</x:v>
       </x:c>
-      <x:c r="F23" s="14" t="str">
+      <x:c r="F26" s="14" t="str">
         <x:v>https://search.jd.com/Search?keyword=%E7%83%AD%E7%BC%A9%E7%AE%A1%201mm%202mm%203mm%205mm%20Kapton%20%E9%AB%98%E6%B8%A9%E8%83%B6%E5%B8%A6</x:v>
       </x:c>
-      <x:c r="G23" s="14" t="str">
+      <x:c r="G26" s="14" t="str">
         <x:v>https://s.taobao.com/search?q=%E7%83%AD%E7%BC%A9%E7%AE%A1%201mm%202mm%203mm%205mm%20Kapton%20%E9%AB%98%E6%B8%A9%E8%83%B6%E5%B8%A6</x:v>
       </x:c>
-      <x:c r="H23" s="14" t="str">
+      <x:c r="H26" s="14" t="str">
         <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=%E7%83%AD%E7%BC%A9%E7%AE%A1%201mm%202mm%203mm%205mm%20Kapton%20%E9%AB%98%E6%B8%A9%E8%83%B6%E5%B8%A6</x:v>
       </x:c>
     </x:row>

--- a/Atlas_Rover_Mk1_制造图纸包_V1.0/采购执行表_Atlas_Rover_Mk1_V1.0.xlsx
+++ b/Atlas_Rover_Mk1_制造图纸包_V1.0/采购执行表_Atlas_Rover_Mk1_V1.0.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="采买执行" sheetId="1" r:id="Rdfa99a0af6d2449b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="采买执行" sheetId="1" r:id="Re122c7aa899f4d42"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -464,7 +464,7 @@
         <x:v>N20 金属减速电机</x:v>
       </x:c>
       <x:c r="B7" s="14" t="str">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C7" s="14" t="str">
         <x:v>必买</x:v>
@@ -473,7 +473,7 @@
         <x:v>N20 金属减速电机 6V 100RPM 3mm D轴 轴长10mm</x:v>
       </x:c>
       <x:c r="E7" s="14" t="str">
-        <x:v>100 RPM 更适合桌面慢速巡游；150 RPM 可用 PWM 限速。Mk.1 不需要编码器版本，除非你要做里程计。</x:v>
+        <x:v>四电机四轮方案使用 4 个 N20；100 RPM 更适合桌面慢速巡游，150 RPM 必须用 PWM 限速。Mk.1 不需要编码器版本。</x:v>
       </x:c>
       <x:c r="F7" s="14" t="str">
         <x:v>https://search.jd.com/Search?keyword=N20%20%E9%87%91%E5%B1%9E%E5%87%8F%E9%80%9F%E7%94%B5%E6%9C%BA%206V%20100RPM%203mm%20D%E8%BD%B4%20%E8%BD%B4%E9%95%BF10mm</x:v>
@@ -490,7 +490,7 @@
         <x:v>DRV8833 双路 H 桥电机驱动板（必备）</x:v>
       </x:c>
       <x:c r="B8" s="14" t="str">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C8" s="14" t="str">
         <x:v>必买</x:v>
@@ -499,7 +499,7 @@
         <x:v>DRV8833 双路 H桥 电机驱动模块 迷你</x:v>
       </x:c>
       <x:c r="E8" s="14" t="str">
-        <x:v>这就是解决“ESP32 不能直接带电机”的必备板子。底盘控制板/PCA9685 只给控制信号，DRV8833 才负责给 N20 电机输出电流。VM 接电机 5 V 升压支路，逻辑电平接 3.3 V，必须共地。</x:v>
+        <x:v>四电机方案前后各一块 DRV8833：前板驱动左前/右前，后板驱动左后/右后；XIAO D2-D5 同时接到两块板输入。不要用一块 DRV8833 长期并联四个电机。</x:v>
       </x:c>
       <x:c r="F8" s="14" t="str">
         <x:v>https://search.jd.com/Search?keyword=DRV8833%20%E5%8F%8C%E8%B7%AF%20H%E6%A1%A5%20%E7%94%B5%E6%9C%BA%E9%A9%B1%E5%8A%A8%E6%A8%A1%E5%9D%97%20%E8%BF%B7%E4%BD%A0</x:v>
@@ -542,16 +542,16 @@
         <x:v>N20 轮胎</x:v>
       </x:c>
       <x:c r="B10" s="14" t="str">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C10" s="14" t="str">
-        <x:v>必买</x:v>
+        <x:v>备选</x:v>
       </x:c>
       <x:c r="D10" s="14" t="str">
         <x:v>N20 轮胎 34mm 3mm D形孔 橡胶轮</x:v>
       </x:c>
       <x:c r="E10" s="14" t="str">
-        <x:v>43 mm 轮也能用，但要抬高前保险杠，并且速度和外宽都会增加。</x:v>
+        <x:v>若 64T 齿轮轮方案打滑或偏摆严重，可回退成 4 个 N20 橡胶轮；43 mm 轮会增加速度和外宽。</x:v>
       </x:c>
       <x:c r="F10" s="14" t="str">
         <x:v>https://search.jd.com/Search?keyword=N20%20%E8%BD%AE%E8%83%8E%2034mm%203mm%20D%E5%BD%A2%E5%AD%94%20%E6%A9%A1%E8%83%B6%E8%BD%AE</x:v>
@@ -568,16 +568,16 @@
         <x:v>64T 钢齿轮轮芯（备选）</x:v>
       </x:c>
       <x:c r="B11" s="14" t="str">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C11" s="14" t="str">
-        <x:v>备选</x:v>
+        <x:v>必买</x:v>
       </x:c>
       <x:c r="D11" s="14" t="str">
         <x:v>64T 钢齿轮 3mm D孔 30mm 机器人 小车</x:v>
       </x:c>
       <x:c r="E11" s="14" t="str">
-        <x:v>仅在买不到合适 N20 橡胶轮时使用。钢齿轮不能默认直接套 N20，必须确认孔径/孔型；外圈建议套 O 型圈或热缩胶圈增加摩擦。</x:v>
+        <x:v>当前采用 64T 齿轮四轮方案。必须确认 3 mm D 孔可直接压入 N20 轴；外圈建议套 O 型圈或热缩胶圈增加摩擦。</x:v>
       </x:c>
       <x:c r="F11" s="14" t="str">
         <x:v>https://search.jd.com/Search?keyword=64T%20%E9%92%A2%E9%BD%BF%E8%BD%AE%203mm%20D%E5%AD%94%2030mm%20%E6%9C%BA%E5%99%A8%E4%BA%BA%20%E5%B0%8F%E8%BD%A6</x:v>
@@ -594,7 +594,7 @@
         <x:v>3 mm D 孔轮毂或夹紧适配器</x:v>
       </x:c>
       <x:c r="B12" s="14" t="str">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C12" s="14" t="str">
         <x:v>备选</x:v>
@@ -603,7 +603,7 @@
         <x:v>3mm D孔 轮毂 N20 电机 联轴器 M2 固定</x:v>
       </x:c>
       <x:c r="E12" s="14" t="str">
-        <x:v>64T 齿轮若不是 3 mm D 孔直连，必须用轮毂/夹片转接；不建议只用胶水粘。</x:v>
+        <x:v>若 64T 齿轮不是 3 mm D 孔直连，必须用轮毂/夹片转接；不建议只用胶水粘。</x:v>
       </x:c>
       <x:c r="F12" s="14" t="str">
         <x:v>https://search.jd.com/Search?keyword=3mm%20D%E5%AD%94%20%E8%BD%AE%E6%AF%82%20N20%20%E7%94%B5%E6%9C%BA%20%E8%81%94%E8%BD%B4%E5%99%A8%20M2%20%E5%9B%BA%E5%AE%9A</x:v>
@@ -620,16 +620,16 @@
         <x:v>齿轮外圈防滑圈</x:v>
       </x:c>
       <x:c r="B13" s="14" t="str">
-        <x:v>2-4</x:v>
+        <x:v>4-8</x:v>
       </x:c>
       <x:c r="C13" s="14" t="str">
-        <x:v>备选</x:v>
+        <x:v>必买</x:v>
       </x:c>
       <x:c r="D13" s="14" t="str">
         <x:v>橡胶 O型圈 热缩管 30mm 35mm 轮胎 防滑</x:v>
       </x:c>
       <x:c r="E13" s="14" t="str">
-        <x:v>钢齿轮直接接触桌面会滑、响、伤桌面；外圈必须加橡胶圈或热缩圈。</x:v>
+        <x:v>钢齿轮直接接触桌面会滑、响、伤桌面；四个齿轮外圈都要加橡胶圈或热缩圈。</x:v>
       </x:c>
       <x:c r="F13" s="14" t="str">
         <x:v>https://search.jd.com/Search?keyword=%E6%A9%A1%E8%83%B6%20O%E5%9E%8B%E5%9C%88%20%E7%83%AD%E7%BC%A9%E7%AE%A1%2030mm%2035mm%20%E8%BD%AE%E8%83%8E%20%E9%98%B2%E6%BB%91</x:v>
@@ -649,13 +649,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C14" s="14" t="str">
-        <x:v>必买</x:v>
+        <x:v>备选</x:v>
       </x:c>
       <x:c r="D14" s="14" t="str">
         <x:v>迷你万向轮 10mm 15mm 球形 小车</x:v>
       </x:c>
       <x:c r="E14" s="14" t="str">
-        <x:v>前置万向轮能让第一版结构更简单。若底盘不水平，可加 1-2 mm 垫片。</x:v>
+        <x:v>四电机四轮方案不把万向轮作为主支撑；可保留用于临时两轮回退方案或台架调试。</x:v>
       </x:c>
       <x:c r="F14" s="14" t="str">
         <x:v>https://search.jd.com/Search?keyword=%E8%BF%B7%E4%BD%A0%E4%B8%87%E5%90%91%E8%BD%AE%2010mm%2015mm%20%E7%90%83%E5%BD%A2%20%E5%B0%8F%E8%BD%A6</x:v>
@@ -681,7 +681,7 @@
         <x:v>18650 锂电池 3.7V 2600mAh 带保护板 持续放电3A</x:v>
       </x:c>
       <x:c r="E15" s="14" t="str">
-        <x:v>裸电芯约 18 x 65 mm；带保护板或尖头电芯可能更长。避免虚标容量电池，电机启动电流会拉低电压。</x:v>
+        <x:v>四个 N20 启动电流更高，避免虚标容量电池；若电机启动导致重启，优先更换高倍率电芯或降低 PWM。</x:v>
       </x:c>
       <x:c r="F15" s="14" t="str">
         <x:v>https://search.jd.com/Search?keyword=18650%20%E9%94%82%E7%94%B5%E6%B1%A0%203.7V%202600mAh%20%E5%B8%A6%E4%BF%9D%E6%8A%A4%E6%9D%BF%20%E6%8C%81%E7%BB%AD%E6%94%BE%E7%94%B53A</x:v>
@@ -733,7 +733,7 @@
         <x:v>锂电池升压模块 3.7V转5V 2A 3A</x:v>
       </x:c>
       <x:c r="E17" s="14" t="str">
-        <x:v>只给电机支路使用。不要让电机电流经过 ESP32 的 3.3 V 电源轨。若两个 N20 堵转明显，优先换更大电流模块。</x:v>
+        <x:v>四个 N20 只从电机支路取电，不要让电机电流经过 ESP32/DualEye。若启动掉压，优先换更大电流模块并降低 PWM。</x:v>
       </x:c>
       <x:c r="F17" s="14" t="str">
         <x:v>https://search.jd.com/Search?keyword=%E9%94%82%E7%94%B5%E6%B1%A0%E5%8D%87%E5%8E%8B%E6%A8%A1%E5%9D%97%203.7V%E8%BD%AC5V%202A%203A</x:v>

--- a/Atlas_Rover_Mk1_制造图纸包_V1.0/采购执行表_Atlas_Rover_Mk1_V1.0.xlsx
+++ b/Atlas_Rover_Mk1_制造图纸包_V1.0/采购执行表_Atlas_Rover_Mk1_V1.0.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="采买执行" sheetId="1" r:id="Re122c7aa899f4d42"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="采买执行" sheetId="1" r:id="R3974c4ecb339423a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -421,7 +421,7 @@
         <x:v>ESP32-S3-DualEye-Touch-LCD-1.28 Waveshare 双眼 屏 开发板</x:v>
       </x:c>
       <x:c r="E5" s="14" t="str">
-        <x:v>官方宽度 93.5 mm。Mk.1 中作为车头双眼/HMI/语音主控，通过 UART 给底盘板下发安全运动意图，不直接带电机。板上已有麦克风、音频编解码/功放和喇叭接口；未集成可做车灯的 RGB/WS2812 灯。</x:v>
+        <x:v>官方宽度 93.5 mm。可作为车头双眼显示；可通过 GPIO/I2C/PWM 扩展控制电机驱动，但不能直接带电机。板上已有麦克风、音频编解码/功放和喇叭接口；未集成可做车灯的 RGB/WS2812 灯。</x:v>
       </x:c>
       <x:c r="F5" s="14" t="str">
         <x:v>https://search.jd.com/Search?keyword=ESP32-S3-DualEye-Touch-LCD-1.28%20Waveshare%20%E5%8F%8C%E7%9C%BC%20%E5%B1%8F%20%E5%BC%80%E5%8F%91%E6%9D%BF</x:v>
@@ -447,7 +447,7 @@
         <x:v>Seeed XIAO ESP32C3 开发板</x:v>
       </x:c>
       <x:c r="E6" s="14" t="str">
-        <x:v>Mk.1 推荐底盘板。负责接收 DualEye UART 的 AR1 指令，执行限速、短时开环差速和超时停车。可用 ESP32-C3 SuperMini 替代，但需要按实物重核引脚。</x:v>
+        <x:v>双板方案的底盘控制器。接收 DualEye UART 指令，执行电机限速、超时停车和 DRV8833 PWM/方向控制；ESP32-C3 SuperMini 可替代但必须重核引脚。</x:v>
       </x:c>
       <x:c r="F6" s="14" t="str">
         <x:v>https://search.jd.com/Search?keyword=Seeed%20XIAO%20ESP32C3%20%E5%BC%80%E5%8F%91%E6%9D%BF</x:v>
@@ -499,7 +499,7 @@
         <x:v>DRV8833 双路 H桥 电机驱动模块 迷你</x:v>
       </x:c>
       <x:c r="E8" s="14" t="str">
-        <x:v>四电机方案前后各一块 DRV8833：前板驱动左前/右前，后板驱动左后/右后；XIAO D2-D5 同时接到两块板输入。不要用一块 DRV8833 长期并联四个电机。</x:v>
+        <x:v>四电机方案前后各一块 DRV8833：前板驱动左前/右前，后板驱动左后/右后；XIAO D2-D5 同时接到两块板输入。前后同侧电机作为同一逻辑侧，不要用一块 DRV8833 长期并联四个电机。</x:v>
       </x:c>
       <x:c r="F8" s="14" t="str">
         <x:v>https://search.jd.com/Search?keyword=DRV8833%20%E5%8F%8C%E8%B7%AF%20H%E6%A1%A5%20%E7%94%B5%E6%9C%BA%E9%A9%B1%E5%8A%A8%E6%A8%A1%E5%9D%97%20%E8%BF%B7%E4%BD%A0</x:v>
@@ -525,7 +525,7 @@
         <x:v>PCA9685 16路 PWM 舵机驱动模块 I2C 迷你</x:v>
       </x:c>
       <x:c r="E9" s="14" t="str">
-        <x:v>这是底盘板侧可选控制信号扩展板，不是电机驱动板。若底盘控制板已有 4 个可用 PWM/DIR GPIO，可省略。</x:v>
+        <x:v>这是底盘板侧可选控制信号扩展板，不是电机驱动板。当前 XIAO D2-D5 可直接扇出到前/后两块 DRV8833，一般可省略；若底盘板 GPIO/PWM 不够再加。</x:v>
       </x:c>
       <x:c r="F9" s="14" t="str">
         <x:v>https://search.jd.com/Search?keyword=PCA9685%2016%E8%B7%AF%20PWM%20%E8%88%B5%E6%9C%BA%E9%A9%B1%E5%8A%A8%E6%A8%A1%E5%9D%97%20I2C%20%E8%BF%B7%E4%BD%A0</x:v>
@@ -577,7 +577,7 @@
         <x:v>64T 钢齿轮 3mm D孔 30mm 机器人 小车</x:v>
       </x:c>
       <x:c r="E11" s="14" t="str">
-        <x:v>当前采用 64T 齿轮四轮方案。必须确认 3 mm D 孔可直接压入 N20 轴；外圈建议套 O 型圈或热缩胶圈增加摩擦。</x:v>
+        <x:v>当前采用 64T 齿轮四轮方案。必须确认 3 mm D 孔可直接压入 N20 轴；每个齿轮直接装在对应 N20 轴上，不使用贯穿通轴；外圈建议套 O 型圈或热缩胶圈增加摩擦。</x:v>
       </x:c>
       <x:c r="F11" s="14" t="str">
         <x:v>https://search.jd.com/Search?keyword=64T%20%E9%92%A2%E9%BD%BF%E8%BD%AE%203mm%20D%E5%AD%94%2030mm%20%E6%9C%BA%E5%99%A8%E4%BA%BA%20%E5%B0%8F%E8%BD%A6</x:v>
@@ -678,19 +678,19 @@
         <x:v>必买</x:v>
       </x:c>
       <x:c r="D15" s="14" t="str">
-        <x:v>18650 锂电池 3.7V 2600mAh 带保护板 持续放电3A</x:v>
+        <x:v>18650 锂电池 3.7V 高倍率 持续放电8A 带保护板</x:v>
       </x:c>
       <x:c r="E15" s="14" t="str">
         <x:v>四个 N20 启动电流更高，避免虚标容量电池；若电机启动导致重启，优先更换高倍率电芯或降低 PWM。</x:v>
       </x:c>
       <x:c r="F15" s="14" t="str">
-        <x:v>https://search.jd.com/Search?keyword=18650%20%E9%94%82%E7%94%B5%E6%B1%A0%203.7V%202600mAh%20%E5%B8%A6%E4%BF%9D%E6%8A%A4%E6%9D%BF%20%E6%8C%81%E7%BB%AD%E6%94%BE%E7%94%B53A</x:v>
+        <x:v>https://search.jd.com/Search?keyword=18650%20%E9%94%82%E7%94%B5%E6%B1%A0%203.7V%20%E9%AB%98%E5%80%8D%E7%8E%87%20%E6%8C%81%E7%BB%AD%E6%94%BE%E7%94%B58A%20%E5%B8%A6%E4%BF%9D%E6%8A%A4%E6%9D%BF</x:v>
       </x:c>
       <x:c r="G15" s="14" t="str">
-        <x:v>https://s.taobao.com/search?q=18650%20%E9%94%82%E7%94%B5%E6%B1%A0%203.7V%202600mAh%20%E5%B8%A6%E4%BF%9D%E6%8A%A4%E6%9D%BF%20%E6%8C%81%E7%BB%AD%E6%94%BE%E7%94%B53A</x:v>
+        <x:v>https://s.taobao.com/search?q=18650%20%E9%94%82%E7%94%B5%E6%B1%A0%203.7V%20%E9%AB%98%E5%80%8D%E7%8E%87%20%E6%8C%81%E7%BB%AD%E6%94%BE%E7%94%B58A%20%E5%B8%A6%E4%BF%9D%E6%8A%A4%E6%9D%BF</x:v>
       </x:c>
       <x:c r="H15" s="14" t="str">
-        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=18650%20%E9%94%82%E7%94%B5%E6%B1%A0%203.7V%202600mAh%20%E5%B8%A6%E4%BF%9D%E6%8A%A4%E6%9D%BF%20%E6%8C%81%E7%BB%AD%E6%94%BE%E7%94%B53A</x:v>
+        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=18650%20%E9%94%82%E7%94%B5%E6%B1%A0%203.7V%20%E9%AB%98%E5%80%8D%E7%8E%87%20%E6%8C%81%E7%BB%AD%E6%94%BE%E7%94%B58A%20%E5%B8%A6%E4%BF%9D%E6%8A%A4%E6%9D%BF</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="42" customHeight="1">
@@ -730,19 +730,19 @@
         <x:v>必买</x:v>
       </x:c>
       <x:c r="D17" s="14" t="str">
-        <x:v>锂电池升压模块 3.7V转5V 2A 3A</x:v>
+        <x:v>锂电池升压模块 3.7V转5V 5A 大电流</x:v>
       </x:c>
       <x:c r="E17" s="14" t="str">
         <x:v>四个 N20 只从电机支路取电，不要让电机电流经过 ESP32/DualEye。若启动掉压，优先换更大电流模块并降低 PWM。</x:v>
       </x:c>
       <x:c r="F17" s="14" t="str">
-        <x:v>https://search.jd.com/Search?keyword=%E9%94%82%E7%94%B5%E6%B1%A0%E5%8D%87%E5%8E%8B%E6%A8%A1%E5%9D%97%203.7V%E8%BD%AC5V%202A%203A</x:v>
+        <x:v>https://search.jd.com/Search?keyword=%E9%94%82%E7%94%B5%E6%B1%A0%E5%8D%87%E5%8E%8B%E6%A8%A1%E5%9D%97%203.7V%E8%BD%AC5V%205A%20%E5%A4%A7%E7%94%B5%E6%B5%81</x:v>
       </x:c>
       <x:c r="G17" s="14" t="str">
-        <x:v>https://s.taobao.com/search?q=%E9%94%82%E7%94%B5%E6%B1%A0%E5%8D%87%E5%8E%8B%E6%A8%A1%E5%9D%97%203.7V%E8%BD%AC5V%202A%203A</x:v>
+        <x:v>https://s.taobao.com/search?q=%E9%94%82%E7%94%B5%E6%B1%A0%E5%8D%87%E5%8E%8B%E6%A8%A1%E5%9D%97%203.7V%E8%BD%AC5V%205A%20%E5%A4%A7%E7%94%B5%E6%B5%81</x:v>
       </x:c>
       <x:c r="H17" s="14" t="str">
-        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=%E9%94%82%E7%94%B5%E6%B1%A0%E5%8D%87%E5%8E%8B%E6%A8%A1%E5%9D%97%203.7V%E8%BD%AC5V%202A%203A</x:v>
+        <x:v>https://mobile.yangkeduo.com/search_result.html?search_key=%E9%94%82%E7%94%B5%E6%B1%A0%E5%8D%87%E5%8E%8B%E6%A8%A1%E5%9D%97%203.7V%E8%BD%AC5V%205A%20%E5%A4%A7%E7%94%B5%E6%B5%81</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="42" customHeight="1">
